--- a/raw/Cải tiến nhập dữ liệu chung vào file MPnew 10.07.2026.xlsx
+++ b/raw/Cải tiến nhập dữ liệu chung vào file MPnew 10.07.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Setup\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{8438F1FB-476F-44D7-9695-086D54B8D6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5E40724-70B5-42EB-9313-224C86852C8D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD33CD63-01A4-4C2E-BDC6-E56B9DE986AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19310" yWindow="1950" windowWidth="19420" windowHeight="10300" tabRatio="703" firstSheet="1" activeTab="1" xr2:uid="{EF1EAAF0-F653-4155-9EE7-30B01C7CE0E3}"/>
   </bookViews>
@@ -682,7 +682,7 @@
     <t>Công thức tính của quần, đồng phục ngắn tay/dài tay, mũ: (bao gồm cả đồng phục phòng an ninh)</t>
   </si>
   <si>
-    <t>Công thức tính giày, giày bảo hộ loại 2, áo polo, áo khoác (bao gồm cả đồng phục phòng an ninh)</t>
+    <t>Công thức tính giày, giày bảo hộ loại 2, áo khoác (bao gồm cả đồng phục phòng an ninh)</t>
   </si>
   <si>
     <t xml:space="preserve">      Số người mới x đơn giá x 2(cái)</t>
@@ -718,6 +718,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
       <t xml:space="preserve">Chỉ phát </t>
     </r>
     <r>
@@ -725,22 +730,12 @@
         <sz val="11"/>
         <color rgb="FF4EA72E"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
       </rPr>
-      <t>đồng phục ngắn tay</t>
+      <t>đồng phục ngắn tay hoặc áo polo:</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">      Số người mới x đơn giá đồng phục ngắn tay x 2(cái)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Số người mới x đơn giá đồng phục ngắn tay hoặc áo polo x 2(cái)</t>
   </si>
   <si>
     <r>
@@ -816,6 +811,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
       <t xml:space="preserve">Phát </t>
     </r>
     <r>
@@ -823,22 +823,12 @@
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
       </rPr>
-      <t>cả đồng phục ngắn tay và dài tay</t>
+      <t>cả đồng phục ngắn tay hoặc áo polo và dài tay (tổng 4 cái)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">      Số người mới x (đơn giá đồng phục ngắn tay x 2(cái) + đơn giá đồng phục dài tay x 2(cái))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Số người mới x (đơn giá đồng phục ngắn tay hoặc áo polo x 2(cái) + đơn giá đồng phục dài tay x 2(cái))</t>
   </si>
   <si>
     <r>
@@ -881,7 +871,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">      (Số người mới từ tháng 1) x đơn giá đồng phục ngắn tay x 2(cái)</t>
+    <t xml:space="preserve">      (Số người mới từ tháng 1) x đơn giá đồng phục ngắn tay hoặc áo polo x 2(cái)</t>
   </si>
   <si>
     <t>Chi phí cốc xếp</t>
@@ -3526,7 +3516,7 @@
     <numFmt numFmtId="164" formatCode="0_ "/>
     <numFmt numFmtId="165" formatCode="#,##0."/>
   </numFmts>
-  <fonts count="65">
+  <fonts count="67">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3968,6 +3958,16 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EA72E"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -4096,7 +4096,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4255,12 +4255,25 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="55" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="51" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="57" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4273,18 +4286,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -18486,52 +18487,52 @@
       <c r="E1" t="s">
         <v>821</v>
       </c>
-      <c r="F1" s="112" t="s">
+      <c r="F1" s="107" t="s">
         <v>822</v>
       </c>
-      <c r="G1" s="112" t="s">
+      <c r="G1" s="107" t="s">
         <v>823</v>
       </c>
-      <c r="H1" s="112" t="s">
+      <c r="H1" s="107" t="s">
         <v>824</v>
       </c>
-      <c r="I1" s="112" t="s">
+      <c r="I1" s="107" t="s">
         <v>825</v>
       </c>
-      <c r="J1" s="112" t="s">
+      <c r="J1" s="107" t="s">
         <v>826</v>
       </c>
-      <c r="K1" s="112" t="s">
+      <c r="K1" s="107" t="s">
         <v>827</v>
       </c>
-      <c r="L1" s="112" t="s">
+      <c r="L1" s="107" t="s">
         <v>828</v>
       </c>
-      <c r="M1" s="112" t="s">
+      <c r="M1" s="107" t="s">
         <v>829</v>
       </c>
-      <c r="N1" s="112" t="s">
+      <c r="N1" s="107" t="s">
         <v>830</v>
       </c>
-      <c r="O1" s="112" t="s">
+      <c r="O1" s="107" t="s">
         <v>831</v>
       </c>
-      <c r="P1" s="112" t="s">
+      <c r="P1" s="107" t="s">
         <v>832</v>
       </c>
-      <c r="Q1" s="112" t="s">
+      <c r="Q1" s="107" t="s">
         <v>833</v>
       </c>
-      <c r="R1" s="112" t="s">
+      <c r="R1" s="107" t="s">
         <v>834</v>
       </c>
-      <c r="S1" s="112" t="s">
+      <c r="S1" s="107" t="s">
         <v>835</v>
       </c>
-      <c r="T1" s="112" t="s">
+      <c r="T1" s="107" t="s">
         <v>836</v>
       </c>
-      <c r="U1" s="112" t="s">
+      <c r="U1" s="107" t="s">
         <v>837</v>
       </c>
     </row>
@@ -18551,32 +18552,32 @@
       <c r="E2" t="s">
         <v>262</v>
       </c>
-      <c r="F2" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I2" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112" t="s">
+      <c r="F2" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I2" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="107"/>
+      <c r="R2" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S2" s="107"/>
+      <c r="T2" s="107"/>
+      <c r="U2" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -18596,32 +18597,32 @@
       <c r="E3" t="s">
         <v>262</v>
       </c>
-      <c r="F3" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I3" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J3" s="112"/>
-      <c r="K3" s="112"/>
-      <c r="L3" s="112"/>
-      <c r="M3" s="112"/>
-      <c r="N3" s="112"/>
-      <c r="O3" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="112"/>
-      <c r="R3" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S3" s="112"/>
-      <c r="T3" s="112"/>
-      <c r="U3" s="112" t="s">
+      <c r="F3" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I3" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P3" s="107"/>
+      <c r="Q3" s="107"/>
+      <c r="R3" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S3" s="107"/>
+      <c r="T3" s="107"/>
+      <c r="U3" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -18641,32 +18642,32 @@
       <c r="E4" t="s">
         <v>262</v>
       </c>
-      <c r="F4" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I4" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112" t="s">
+      <c r="F4" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I4" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="107"/>
+      <c r="N4" s="107"/>
+      <c r="O4" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P4" s="107"/>
+      <c r="Q4" s="107"/>
+      <c r="R4" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S4" s="107"/>
+      <c r="T4" s="107"/>
+      <c r="U4" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -18686,32 +18687,32 @@
       <c r="E5" t="s">
         <v>262</v>
       </c>
-      <c r="F5" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G5" s="112"/>
-      <c r="H5" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I5" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J5" s="112"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
-      <c r="N5" s="112"/>
-      <c r="O5" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S5" s="112"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="112" t="s">
+      <c r="F5" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I5" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P5" s="107"/>
+      <c r="Q5" s="107"/>
+      <c r="R5" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S5" s="107"/>
+      <c r="T5" s="107"/>
+      <c r="U5" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -18731,32 +18732,32 @@
       <c r="E6" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G6" s="112"/>
-      <c r="H6" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I6" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J6" s="112"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="112"/>
-      <c r="O6" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P6" s="112"/>
-      <c r="Q6" s="112"/>
-      <c r="R6" s="112"/>
-      <c r="S6" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T6" s="112"/>
-      <c r="U6" s="112" t="s">
+      <c r="F6" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I6" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J6" s="107"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="107"/>
+      <c r="O6" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="107"/>
+      <c r="S6" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T6" s="107"/>
+      <c r="U6" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -18776,34 +18777,34 @@
       <c r="E7" t="s">
         <v>262</v>
       </c>
-      <c r="F7" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I7" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J7" s="112"/>
-      <c r="K7" s="112"/>
-      <c r="L7" s="112"/>
-      <c r="M7" s="112"/>
-      <c r="N7" s="112"/>
-      <c r="O7" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P7" s="112"/>
-      <c r="Q7" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="R7" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S7" s="112"/>
-      <c r="T7" s="112"/>
-      <c r="U7" s="112" t="s">
+      <c r="F7" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I7" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P7" s="107"/>
+      <c r="Q7" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="R7" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S7" s="107"/>
+      <c r="T7" s="107"/>
+      <c r="U7" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -18823,32 +18824,32 @@
       <c r="E8" t="s">
         <v>262</v>
       </c>
-      <c r="F8" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I8" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J8" s="112"/>
-      <c r="K8" s="112"/>
-      <c r="L8" s="112"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="112"/>
-      <c r="O8" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P8" s="112"/>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="112"/>
-      <c r="S8" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T8" s="112"/>
-      <c r="U8" s="112"/>
+      <c r="F8" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I8" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J8" s="107"/>
+      <c r="K8" s="107"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="107"/>
+      <c r="N8" s="107"/>
+      <c r="O8" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="107"/>
+      <c r="R8" s="107"/>
+      <c r="S8" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T8" s="107"/>
+      <c r="U8" s="107"/>
     </row>
     <row r="9" spans="1:21" ht="15">
       <c r="A9">
@@ -18866,32 +18867,32 @@
       <c r="E9" t="s">
         <v>262</v>
       </c>
-      <c r="F9" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I9" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J9" s="112"/>
-      <c r="K9" s="112"/>
-      <c r="L9" s="112"/>
-      <c r="M9" s="112"/>
-      <c r="N9" s="112"/>
-      <c r="O9" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P9" s="112"/>
-      <c r="Q9" s="112"/>
-      <c r="R9" s="112"/>
-      <c r="S9" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T9" s="112"/>
-      <c r="U9" s="112"/>
+      <c r="F9" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I9" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J9" s="107"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="107"/>
+      <c r="M9" s="107"/>
+      <c r="N9" s="107"/>
+      <c r="O9" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P9" s="107"/>
+      <c r="Q9" s="107"/>
+      <c r="R9" s="107"/>
+      <c r="S9" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T9" s="107"/>
+      <c r="U9" s="107"/>
     </row>
     <row r="10" spans="1:21" ht="15">
       <c r="A10">
@@ -18909,32 +18910,32 @@
       <c r="E10" t="s">
         <v>262</v>
       </c>
-      <c r="F10" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I10" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J10" s="112"/>
-      <c r="K10" s="112"/>
-      <c r="L10" s="112"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
-      <c r="O10" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P10" s="112"/>
-      <c r="Q10" s="112"/>
-      <c r="R10" s="112"/>
-      <c r="S10" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T10" s="112"/>
-      <c r="U10" s="112"/>
+      <c r="F10" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G10" s="107"/>
+      <c r="H10" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I10" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J10" s="107"/>
+      <c r="K10" s="107"/>
+      <c r="L10" s="107"/>
+      <c r="M10" s="107"/>
+      <c r="N10" s="107"/>
+      <c r="O10" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P10" s="107"/>
+      <c r="Q10" s="107"/>
+      <c r="R10" s="107"/>
+      <c r="S10" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T10" s="107"/>
+      <c r="U10" s="107"/>
     </row>
     <row r="11" spans="1:21" ht="15">
       <c r="A11">
@@ -18952,32 +18953,32 @@
       <c r="E11" t="s">
         <v>262</v>
       </c>
-      <c r="F11" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I11" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J11" s="112"/>
-      <c r="K11" s="112"/>
-      <c r="L11" s="112"/>
-      <c r="M11" s="112"/>
-      <c r="N11" s="112"/>
-      <c r="O11" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P11" s="112"/>
-      <c r="Q11" s="112"/>
-      <c r="R11" s="112"/>
-      <c r="S11" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T11" s="112"/>
-      <c r="U11" s="112"/>
+      <c r="F11" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G11" s="107"/>
+      <c r="H11" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I11" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J11" s="107"/>
+      <c r="K11" s="107"/>
+      <c r="L11" s="107"/>
+      <c r="M11" s="107"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P11" s="107"/>
+      <c r="Q11" s="107"/>
+      <c r="R11" s="107"/>
+      <c r="S11" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T11" s="107"/>
+      <c r="U11" s="107"/>
     </row>
     <row r="12" spans="1:21" ht="15">
       <c r="A12">
@@ -18995,32 +18996,32 @@
       <c r="E12" t="s">
         <v>262</v>
       </c>
-      <c r="F12" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I12" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J12" s="112"/>
-      <c r="K12" s="112"/>
-      <c r="L12" s="112"/>
-      <c r="M12" s="112"/>
-      <c r="N12" s="112"/>
-      <c r="O12" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P12" s="112"/>
-      <c r="Q12" s="112"/>
-      <c r="R12" s="112"/>
-      <c r="S12" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T12" s="112"/>
-      <c r="U12" s="112"/>
+      <c r="F12" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G12" s="107"/>
+      <c r="H12" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I12" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J12" s="107"/>
+      <c r="K12" s="107"/>
+      <c r="L12" s="107"/>
+      <c r="M12" s="107"/>
+      <c r="N12" s="107"/>
+      <c r="O12" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P12" s="107"/>
+      <c r="Q12" s="107"/>
+      <c r="R12" s="107"/>
+      <c r="S12" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T12" s="107"/>
+      <c r="U12" s="107"/>
     </row>
     <row r="13" spans="1:21" ht="15">
       <c r="A13">
@@ -19038,32 +19039,32 @@
       <c r="E13" t="s">
         <v>262</v>
       </c>
-      <c r="F13" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I13" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J13" s="112"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="112"/>
-      <c r="M13" s="112"/>
-      <c r="N13" s="112"/>
-      <c r="O13" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P13" s="112"/>
-      <c r="Q13" s="112"/>
-      <c r="R13" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S13" s="112"/>
-      <c r="T13" s="112"/>
-      <c r="U13" s="112"/>
+      <c r="F13" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I13" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J13" s="107"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="107"/>
+      <c r="M13" s="107"/>
+      <c r="N13" s="107"/>
+      <c r="O13" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P13" s="107"/>
+      <c r="Q13" s="107"/>
+      <c r="R13" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S13" s="107"/>
+      <c r="T13" s="107"/>
+      <c r="U13" s="107"/>
     </row>
     <row r="14" spans="1:21" ht="15">
       <c r="A14">
@@ -19081,36 +19082,36 @@
       <c r="E14" t="s">
         <v>262</v>
       </c>
-      <c r="F14" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G14" s="112"/>
-      <c r="H14" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I14" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J14" s="112"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="M14" s="112"/>
-      <c r="N14" s="112"/>
-      <c r="O14" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P14" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="112"/>
-      <c r="S14" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T14" s="112"/>
-      <c r="U14" s="112" t="s">
+      <c r="F14" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G14" s="107"/>
+      <c r="H14" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I14" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J14" s="107"/>
+      <c r="K14" s="107"/>
+      <c r="L14" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="M14" s="107"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P14" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q14" s="107"/>
+      <c r="R14" s="107"/>
+      <c r="S14" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T14" s="107"/>
+      <c r="U14" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19130,36 +19131,36 @@
       <c r="E15" t="s">
         <v>262</v>
       </c>
-      <c r="F15" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G15" s="112"/>
-      <c r="H15" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I15" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J15" s="112"/>
-      <c r="K15" s="112"/>
-      <c r="L15" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="M15" s="112"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P15" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q15" s="112"/>
-      <c r="R15" s="112"/>
-      <c r="S15" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T15" s="112"/>
-      <c r="U15" s="112" t="s">
+      <c r="F15" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I15" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J15" s="107"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="M15" s="107"/>
+      <c r="N15" s="107"/>
+      <c r="O15" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P15" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q15" s="107"/>
+      <c r="R15" s="107"/>
+      <c r="S15" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T15" s="107"/>
+      <c r="U15" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19179,32 +19180,32 @@
       <c r="E16" t="s">
         <v>262</v>
       </c>
-      <c r="F16" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G16" s="112"/>
-      <c r="H16" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I16" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J16" s="112"/>
-      <c r="K16" s="112"/>
-      <c r="L16" s="112"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="112"/>
-      <c r="O16" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P16" s="112"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="112"/>
-      <c r="S16" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T16" s="112"/>
-      <c r="U16" s="112" t="s">
+      <c r="F16" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G16" s="107"/>
+      <c r="H16" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I16" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J16" s="107"/>
+      <c r="K16" s="107"/>
+      <c r="L16" s="107"/>
+      <c r="M16" s="107"/>
+      <c r="N16" s="107"/>
+      <c r="O16" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P16" s="107"/>
+      <c r="Q16" s="107"/>
+      <c r="R16" s="107"/>
+      <c r="S16" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T16" s="107"/>
+      <c r="U16" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19224,32 +19225,32 @@
       <c r="E17" t="s">
         <v>262</v>
       </c>
-      <c r="F17" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G17" s="112"/>
-      <c r="H17" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I17" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J17" s="112"/>
-      <c r="K17" s="112"/>
-      <c r="L17" s="112"/>
-      <c r="M17" s="112"/>
-      <c r="N17" s="112"/>
-      <c r="O17" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P17" s="112"/>
-      <c r="Q17" s="112"/>
-      <c r="R17" s="112"/>
-      <c r="S17" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T17" s="112"/>
-      <c r="U17" s="112" t="s">
+      <c r="F17" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G17" s="107"/>
+      <c r="H17" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I17" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J17" s="107"/>
+      <c r="K17" s="107"/>
+      <c r="L17" s="107"/>
+      <c r="M17" s="107"/>
+      <c r="N17" s="107"/>
+      <c r="O17" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P17" s="107"/>
+      <c r="Q17" s="107"/>
+      <c r="R17" s="107"/>
+      <c r="S17" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T17" s="107"/>
+      <c r="U17" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19269,32 +19270,32 @@
       <c r="E18" t="s">
         <v>262</v>
       </c>
-      <c r="F18" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G18" s="112"/>
-      <c r="H18" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I18" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J18" s="112"/>
-      <c r="K18" s="112"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="112"/>
-      <c r="N18" s="112"/>
-      <c r="O18" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
-      <c r="S18" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112" t="s">
+      <c r="F18" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G18" s="107"/>
+      <c r="H18" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I18" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J18" s="107"/>
+      <c r="K18" s="107"/>
+      <c r="L18" s="107"/>
+      <c r="M18" s="107"/>
+      <c r="N18" s="107"/>
+      <c r="O18" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P18" s="107"/>
+      <c r="Q18" s="107"/>
+      <c r="R18" s="107"/>
+      <c r="S18" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T18" s="107"/>
+      <c r="U18" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19314,36 +19315,36 @@
       <c r="E19" t="s">
         <v>262</v>
       </c>
-      <c r="F19" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I19" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P19" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112" t="s">
+      <c r="F19" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G19" s="107"/>
+      <c r="H19" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I19" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J19" s="107"/>
+      <c r="K19" s="107"/>
+      <c r="L19" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="M19" s="107"/>
+      <c r="N19" s="107"/>
+      <c r="O19" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P19" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q19" s="107"/>
+      <c r="R19" s="107"/>
+      <c r="S19" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T19" s="107"/>
+      <c r="U19" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19363,32 +19364,32 @@
       <c r="E20" t="s">
         <v>262</v>
       </c>
-      <c r="F20" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G20" s="112"/>
-      <c r="H20" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I20" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J20" s="112"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="112"/>
-      <c r="M20" s="112"/>
-      <c r="N20" s="112"/>
-      <c r="O20" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P20" s="112"/>
-      <c r="Q20" s="112"/>
-      <c r="R20" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S20" s="112"/>
-      <c r="T20" s="112"/>
-      <c r="U20" s="112"/>
+      <c r="F20" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I20" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J20" s="107"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="107"/>
+      <c r="N20" s="107"/>
+      <c r="O20" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P20" s="107"/>
+      <c r="Q20" s="107"/>
+      <c r="R20" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S20" s="107"/>
+      <c r="T20" s="107"/>
+      <c r="U20" s="107"/>
     </row>
     <row r="21" spans="1:21" ht="15">
       <c r="A21">
@@ -19406,32 +19407,32 @@
       <c r="E21" t="s">
         <v>262</v>
       </c>
-      <c r="F21" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G21" s="112"/>
-      <c r="H21" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I21" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J21" s="112"/>
-      <c r="K21" s="112"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="112"/>
-      <c r="N21" s="112"/>
-      <c r="O21" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
+      <c r="F21" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I21" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J21" s="107"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="107"/>
+      <c r="M21" s="107"/>
+      <c r="N21" s="107"/>
+      <c r="O21" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P21" s="107"/>
+      <c r="Q21" s="107"/>
+      <c r="R21" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S21" s="107"/>
+      <c r="T21" s="107"/>
+      <c r="U21" s="107"/>
     </row>
     <row r="22" spans="1:21" ht="15">
       <c r="A22">
@@ -19449,32 +19450,32 @@
       <c r="E22" t="s">
         <v>262</v>
       </c>
-      <c r="F22" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G22" s="112"/>
-      <c r="H22" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I22" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J22" s="112"/>
-      <c r="K22" s="112"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="112"/>
-      <c r="N22" s="112"/>
-      <c r="O22" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P22" s="112"/>
-      <c r="Q22" s="112"/>
-      <c r="R22" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S22" s="112"/>
-      <c r="T22" s="112"/>
-      <c r="U22" s="112"/>
+      <c r="F22" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G22" s="107"/>
+      <c r="H22" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I22" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J22" s="107"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="107"/>
+      <c r="M22" s="107"/>
+      <c r="N22" s="107"/>
+      <c r="O22" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P22" s="107"/>
+      <c r="Q22" s="107"/>
+      <c r="R22" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S22" s="107"/>
+      <c r="T22" s="107"/>
+      <c r="U22" s="107"/>
     </row>
     <row r="23" spans="1:21" ht="15">
       <c r="A23">
@@ -19492,32 +19493,32 @@
       <c r="E23" t="s">
         <v>262</v>
       </c>
-      <c r="F23" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G23" s="112"/>
-      <c r="H23" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I23" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J23" s="112"/>
-      <c r="K23" s="112"/>
-      <c r="L23" s="112"/>
-      <c r="M23" s="112"/>
-      <c r="N23" s="112"/>
-      <c r="O23" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P23" s="112"/>
-      <c r="Q23" s="112"/>
-      <c r="R23" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S23" s="112"/>
-      <c r="T23" s="112"/>
-      <c r="U23" s="112" t="s">
+      <c r="F23" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G23" s="107"/>
+      <c r="H23" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I23" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J23" s="107"/>
+      <c r="K23" s="107"/>
+      <c r="L23" s="107"/>
+      <c r="M23" s="107"/>
+      <c r="N23" s="107"/>
+      <c r="O23" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P23" s="107"/>
+      <c r="Q23" s="107"/>
+      <c r="R23" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S23" s="107"/>
+      <c r="T23" s="107"/>
+      <c r="U23" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19537,36 +19538,36 @@
       <c r="E24" t="s">
         <v>262</v>
       </c>
-      <c r="F24" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G24" s="112"/>
-      <c r="H24" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I24" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J24" s="112"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="M24" s="112"/>
-      <c r="N24" s="112"/>
-      <c r="O24" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P24" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q24" s="112"/>
-      <c r="R24" s="112"/>
-      <c r="S24" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T24" s="112"/>
-      <c r="U24" s="112"/>
+      <c r="F24" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G24" s="107"/>
+      <c r="H24" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I24" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J24" s="107"/>
+      <c r="K24" s="107"/>
+      <c r="L24" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="M24" s="107"/>
+      <c r="N24" s="107"/>
+      <c r="O24" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P24" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q24" s="107"/>
+      <c r="R24" s="107"/>
+      <c r="S24" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T24" s="107"/>
+      <c r="U24" s="107"/>
     </row>
     <row r="25" spans="1:21" ht="15">
       <c r="A25">
@@ -19584,34 +19585,34 @@
       <c r="E25" t="s">
         <v>264</v>
       </c>
-      <c r="F25" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I25" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J25" s="112"/>
-      <c r="K25" s="112"/>
-      <c r="L25" s="112"/>
-      <c r="M25" s="112"/>
-      <c r="N25" s="112"/>
-      <c r="O25" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P25" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q25" s="112"/>
-      <c r="R25" s="112"/>
-      <c r="S25" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T25" s="112"/>
-      <c r="U25" s="112" t="s">
+      <c r="F25" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I25" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J25" s="107"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="107"/>
+      <c r="M25" s="107"/>
+      <c r="N25" s="107"/>
+      <c r="O25" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P25" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q25" s="107"/>
+      <c r="R25" s="107"/>
+      <c r="S25" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T25" s="107"/>
+      <c r="U25" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19631,32 +19632,32 @@
       <c r="E26" t="s">
         <v>262</v>
       </c>
-      <c r="F26" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G26" s="112"/>
-      <c r="H26" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I26" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J26" s="112"/>
-      <c r="K26" s="112"/>
-      <c r="L26" s="112"/>
-      <c r="M26" s="112"/>
-      <c r="N26" s="112"/>
-      <c r="O26" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P26" s="112"/>
-      <c r="Q26" s="112"/>
-      <c r="R26" s="112"/>
-      <c r="S26" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T26" s="112"/>
-      <c r="U26" s="112" t="s">
+      <c r="F26" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G26" s="107"/>
+      <c r="H26" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I26" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J26" s="107"/>
+      <c r="K26" s="107"/>
+      <c r="L26" s="107"/>
+      <c r="M26" s="107"/>
+      <c r="N26" s="107"/>
+      <c r="O26" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P26" s="107"/>
+      <c r="Q26" s="107"/>
+      <c r="R26" s="107"/>
+      <c r="S26" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T26" s="107"/>
+      <c r="U26" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19676,32 +19677,32 @@
       <c r="E27" t="s">
         <v>262</v>
       </c>
-      <c r="F27" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G27" s="112"/>
-      <c r="H27" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I27" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J27" s="112"/>
-      <c r="K27" s="112"/>
-      <c r="L27" s="112"/>
-      <c r="M27" s="112"/>
-      <c r="N27" s="112"/>
-      <c r="O27" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P27" s="112"/>
-      <c r="Q27" s="112"/>
-      <c r="R27" s="112"/>
-      <c r="S27" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T27" s="112"/>
-      <c r="U27" s="112" t="s">
+      <c r="F27" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G27" s="107"/>
+      <c r="H27" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I27" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J27" s="107"/>
+      <c r="K27" s="107"/>
+      <c r="L27" s="107"/>
+      <c r="M27" s="107"/>
+      <c r="N27" s="107"/>
+      <c r="O27" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P27" s="107"/>
+      <c r="Q27" s="107"/>
+      <c r="R27" s="107"/>
+      <c r="S27" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T27" s="107"/>
+      <c r="U27" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19721,32 +19722,32 @@
       <c r="E28" t="s">
         <v>262</v>
       </c>
-      <c r="F28" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G28" s="112"/>
-      <c r="H28" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I28" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J28" s="112"/>
-      <c r="K28" s="112"/>
-      <c r="L28" s="112"/>
-      <c r="M28" s="112"/>
-      <c r="N28" s="112"/>
-      <c r="O28" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="112"/>
-      <c r="R28" s="112"/>
-      <c r="S28" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T28" s="112"/>
-      <c r="U28" s="112" t="s">
+      <c r="F28" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G28" s="107"/>
+      <c r="H28" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I28" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J28" s="107"/>
+      <c r="K28" s="107"/>
+      <c r="L28" s="107"/>
+      <c r="M28" s="107"/>
+      <c r="N28" s="107"/>
+      <c r="O28" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P28" s="107"/>
+      <c r="Q28" s="107"/>
+      <c r="R28" s="107"/>
+      <c r="S28" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T28" s="107"/>
+      <c r="U28" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -19766,32 +19767,32 @@
       <c r="E29" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G29" s="112"/>
-      <c r="H29" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I29" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J29" s="112"/>
-      <c r="K29" s="112"/>
-      <c r="L29" s="112"/>
-      <c r="M29" s="112"/>
-      <c r="N29" s="112"/>
-      <c r="O29" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P29" s="112"/>
-      <c r="Q29" s="112"/>
-      <c r="R29" s="112"/>
-      <c r="S29" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T29" s="112"/>
-      <c r="U29" s="112"/>
+      <c r="F29" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G29" s="107"/>
+      <c r="H29" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I29" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J29" s="107"/>
+      <c r="K29" s="107"/>
+      <c r="L29" s="107"/>
+      <c r="M29" s="107"/>
+      <c r="N29" s="107"/>
+      <c r="O29" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P29" s="107"/>
+      <c r="Q29" s="107"/>
+      <c r="R29" s="107"/>
+      <c r="S29" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T29" s="107"/>
+      <c r="U29" s="107"/>
     </row>
     <row r="30" spans="1:21" ht="15">
       <c r="A30">
@@ -19809,32 +19810,32 @@
       <c r="E30" t="s">
         <v>262</v>
       </c>
-      <c r="F30" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G30" s="112"/>
-      <c r="H30" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I30" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J30" s="112"/>
-      <c r="K30" s="112"/>
-      <c r="L30" s="112"/>
-      <c r="M30" s="112"/>
-      <c r="N30" s="112"/>
-      <c r="O30" s="112"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="R30" s="112"/>
-      <c r="S30" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T30" s="112"/>
-      <c r="U30" s="112"/>
+      <c r="F30" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G30" s="107"/>
+      <c r="H30" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I30" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J30" s="107"/>
+      <c r="K30" s="107"/>
+      <c r="L30" s="107"/>
+      <c r="M30" s="107"/>
+      <c r="N30" s="107"/>
+      <c r="O30" s="107"/>
+      <c r="P30" s="107"/>
+      <c r="Q30" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="R30" s="107"/>
+      <c r="S30" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T30" s="107"/>
+      <c r="U30" s="107"/>
     </row>
     <row r="31" spans="1:21" ht="15">
       <c r="A31">
@@ -19852,32 +19853,32 @@
       <c r="E31" t="s">
         <v>262</v>
       </c>
-      <c r="F31" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G31" s="112"/>
-      <c r="H31" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I31" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J31" s="112"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="112"/>
-      <c r="R31" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S31" s="112"/>
-      <c r="T31" s="112"/>
-      <c r="U31" s="112"/>
+      <c r="F31" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G31" s="107"/>
+      <c r="H31" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I31" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J31" s="107"/>
+      <c r="K31" s="107"/>
+      <c r="L31" s="107"/>
+      <c r="M31" s="107"/>
+      <c r="N31" s="107"/>
+      <c r="O31" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P31" s="107"/>
+      <c r="Q31" s="107"/>
+      <c r="R31" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S31" s="107"/>
+      <c r="T31" s="107"/>
+      <c r="U31" s="107"/>
     </row>
     <row r="32" spans="1:21" ht="15">
       <c r="A32">
@@ -19895,32 +19896,32 @@
       <c r="E32" t="s">
         <v>262</v>
       </c>
-      <c r="F32" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G32" s="112"/>
-      <c r="H32" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I32" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J32" s="112"/>
-      <c r="K32" s="112"/>
-      <c r="L32" s="112"/>
-      <c r="M32" s="112"/>
-      <c r="N32" s="112"/>
-      <c r="O32" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P32" s="112"/>
-      <c r="Q32" s="112"/>
-      <c r="R32" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S32" s="112"/>
-      <c r="T32" s="112"/>
-      <c r="U32" s="112"/>
+      <c r="F32" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G32" s="107"/>
+      <c r="H32" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I32" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J32" s="107"/>
+      <c r="K32" s="107"/>
+      <c r="L32" s="107"/>
+      <c r="M32" s="107"/>
+      <c r="N32" s="107"/>
+      <c r="O32" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P32" s="107"/>
+      <c r="Q32" s="107"/>
+      <c r="R32" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S32" s="107"/>
+      <c r="T32" s="107"/>
+      <c r="U32" s="107"/>
     </row>
     <row r="33" spans="1:21" ht="15">
       <c r="A33">
@@ -19938,32 +19939,32 @@
       <c r="E33" t="s">
         <v>262</v>
       </c>
-      <c r="F33" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G33" s="112"/>
-      <c r="H33" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I33" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J33" s="112"/>
-      <c r="K33" s="112"/>
-      <c r="L33" s="112"/>
-      <c r="M33" s="112"/>
-      <c r="N33" s="112"/>
-      <c r="O33" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P33" s="112"/>
-      <c r="Q33" s="112"/>
-      <c r="R33" s="112"/>
-      <c r="S33" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T33" s="112"/>
-      <c r="U33" s="112"/>
+      <c r="F33" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G33" s="107"/>
+      <c r="H33" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I33" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J33" s="107"/>
+      <c r="K33" s="107"/>
+      <c r="L33" s="107"/>
+      <c r="M33" s="107"/>
+      <c r="N33" s="107"/>
+      <c r="O33" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P33" s="107"/>
+      <c r="Q33" s="107"/>
+      <c r="R33" s="107"/>
+      <c r="S33" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T33" s="107"/>
+      <c r="U33" s="107"/>
     </row>
     <row r="34" spans="1:21" ht="15">
       <c r="A34">
@@ -19981,32 +19982,32 @@
       <c r="E34" t="s">
         <v>262</v>
       </c>
-      <c r="F34" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G34" s="112"/>
-      <c r="H34" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I34" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J34" s="112"/>
-      <c r="K34" s="112"/>
-      <c r="L34" s="112"/>
-      <c r="M34" s="112"/>
-      <c r="N34" s="112"/>
-      <c r="O34" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P34" s="112"/>
-      <c r="Q34" s="112"/>
-      <c r="R34" s="112"/>
-      <c r="S34" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T34" s="112"/>
-      <c r="U34" s="112"/>
+      <c r="F34" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G34" s="107"/>
+      <c r="H34" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I34" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J34" s="107"/>
+      <c r="K34" s="107"/>
+      <c r="L34" s="107"/>
+      <c r="M34" s="107"/>
+      <c r="N34" s="107"/>
+      <c r="O34" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P34" s="107"/>
+      <c r="Q34" s="107"/>
+      <c r="R34" s="107"/>
+      <c r="S34" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T34" s="107"/>
+      <c r="U34" s="107"/>
     </row>
     <row r="35" spans="1:21" ht="15">
       <c r="A35">
@@ -20024,32 +20025,32 @@
       <c r="E35" t="s">
         <v>262</v>
       </c>
-      <c r="F35" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G35" s="112"/>
-      <c r="H35" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I35" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J35" s="112"/>
-      <c r="K35" s="112"/>
-      <c r="L35" s="112"/>
-      <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
-      <c r="O35" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P35" s="112"/>
-      <c r="Q35" s="112"/>
-      <c r="R35" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S35" s="112"/>
-      <c r="T35" s="112"/>
-      <c r="U35" s="112"/>
+      <c r="F35" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G35" s="107"/>
+      <c r="H35" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I35" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J35" s="107"/>
+      <c r="K35" s="107"/>
+      <c r="L35" s="107"/>
+      <c r="M35" s="107"/>
+      <c r="N35" s="107"/>
+      <c r="O35" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P35" s="107"/>
+      <c r="Q35" s="107"/>
+      <c r="R35" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S35" s="107"/>
+      <c r="T35" s="107"/>
+      <c r="U35" s="107"/>
     </row>
     <row r="36" spans="1:21" ht="15">
       <c r="A36" s="58">
@@ -20067,32 +20068,32 @@
       <c r="E36" t="s">
         <v>262</v>
       </c>
-      <c r="F36" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G36" s="112"/>
-      <c r="H36" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I36" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J36" s="112"/>
-      <c r="K36" s="112"/>
-      <c r="L36" s="112"/>
-      <c r="M36" s="112"/>
-      <c r="N36" s="112"/>
-      <c r="O36" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P36" s="112"/>
-      <c r="Q36" s="112"/>
-      <c r="R36" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S36" s="112"/>
-      <c r="T36" s="112"/>
-      <c r="U36" s="112"/>
+      <c r="F36" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G36" s="107"/>
+      <c r="H36" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I36" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J36" s="107"/>
+      <c r="K36" s="107"/>
+      <c r="L36" s="107"/>
+      <c r="M36" s="107"/>
+      <c r="N36" s="107"/>
+      <c r="O36" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P36" s="107"/>
+      <c r="Q36" s="107"/>
+      <c r="R36" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S36" s="107"/>
+      <c r="T36" s="107"/>
+      <c r="U36" s="107"/>
     </row>
     <row r="37" spans="1:21" ht="15">
       <c r="A37">
@@ -20110,32 +20111,32 @@
       <c r="E37" t="s">
         <v>262</v>
       </c>
-      <c r="F37" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G37" s="112"/>
-      <c r="H37" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I37" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
-      <c r="M37" s="112"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P37" s="112"/>
-      <c r="Q37" s="112"/>
-      <c r="R37" s="112"/>
-      <c r="S37" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T37" s="112"/>
-      <c r="U37" s="112"/>
+      <c r="F37" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G37" s="107"/>
+      <c r="H37" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I37" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J37" s="107"/>
+      <c r="K37" s="107"/>
+      <c r="L37" s="107"/>
+      <c r="M37" s="107"/>
+      <c r="N37" s="107"/>
+      <c r="O37" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P37" s="107"/>
+      <c r="Q37" s="107"/>
+      <c r="R37" s="107"/>
+      <c r="S37" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T37" s="107"/>
+      <c r="U37" s="107"/>
     </row>
     <row r="38" spans="1:21" ht="15">
       <c r="A38">
@@ -20153,32 +20154,32 @@
       <c r="E38" t="s">
         <v>262</v>
       </c>
-      <c r="F38" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G38" s="112"/>
-      <c r="H38" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I38" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J38" s="112"/>
-      <c r="K38" s="112"/>
-      <c r="L38" s="112"/>
-      <c r="M38" s="112"/>
-      <c r="N38" s="112"/>
-      <c r="O38" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P38" s="112"/>
-      <c r="Q38" s="112"/>
-      <c r="R38" s="112"/>
-      <c r="S38" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T38" s="112"/>
-      <c r="U38" s="112"/>
+      <c r="F38" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G38" s="107"/>
+      <c r="H38" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I38" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J38" s="107"/>
+      <c r="K38" s="107"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
+      <c r="S38" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T38" s="107"/>
+      <c r="U38" s="107"/>
     </row>
     <row r="39" spans="1:21" ht="15">
       <c r="A39">
@@ -20196,32 +20197,32 @@
       <c r="E39" t="s">
         <v>262</v>
       </c>
-      <c r="F39" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G39" s="112"/>
-      <c r="H39" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I39" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J39" s="112"/>
-      <c r="K39" s="112"/>
-      <c r="L39" s="112"/>
-      <c r="M39" s="112"/>
-      <c r="N39" s="112"/>
-      <c r="O39" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P39" s="112"/>
-      <c r="Q39" s="112"/>
-      <c r="R39" s="112"/>
-      <c r="S39" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T39" s="112"/>
-      <c r="U39" s="112"/>
+      <c r="F39" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G39" s="107"/>
+      <c r="H39" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I39" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J39" s="107"/>
+      <c r="K39" s="107"/>
+      <c r="L39" s="107"/>
+      <c r="M39" s="107"/>
+      <c r="N39" s="107"/>
+      <c r="O39" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P39" s="107"/>
+      <c r="Q39" s="107"/>
+      <c r="R39" s="107"/>
+      <c r="S39" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T39" s="107"/>
+      <c r="U39" s="107"/>
     </row>
     <row r="40" spans="1:21" ht="15">
       <c r="A40">
@@ -20239,32 +20240,32 @@
       <c r="E40" t="s">
         <v>262</v>
       </c>
-      <c r="F40" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G40" s="112"/>
-      <c r="H40" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I40" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J40" s="112"/>
-      <c r="K40" s="112"/>
-      <c r="L40" s="112"/>
-      <c r="M40" s="112"/>
-      <c r="N40" s="112"/>
-      <c r="O40" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P40" s="112"/>
-      <c r="Q40" s="112"/>
-      <c r="R40" s="112"/>
-      <c r="S40" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T40" s="112"/>
-      <c r="U40" s="112"/>
+      <c r="F40" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G40" s="107"/>
+      <c r="H40" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I40" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J40" s="107"/>
+      <c r="K40" s="107"/>
+      <c r="L40" s="107"/>
+      <c r="M40" s="107"/>
+      <c r="N40" s="107"/>
+      <c r="O40" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P40" s="107"/>
+      <c r="Q40" s="107"/>
+      <c r="R40" s="107"/>
+      <c r="S40" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T40" s="107"/>
+      <c r="U40" s="107"/>
     </row>
     <row r="41" spans="1:21" ht="15">
       <c r="A41">
@@ -20282,32 +20283,32 @@
       <c r="E41" t="s">
         <v>262</v>
       </c>
-      <c r="F41" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G41" s="112"/>
-      <c r="H41" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I41" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J41" s="112"/>
-      <c r="K41" s="112"/>
-      <c r="L41" s="112"/>
-      <c r="M41" s="112"/>
-      <c r="N41" s="112"/>
-      <c r="O41" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P41" s="112"/>
-      <c r="Q41" s="112"/>
-      <c r="R41" s="112"/>
-      <c r="S41" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T41" s="112"/>
-      <c r="U41" s="112"/>
+      <c r="F41" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G41" s="107"/>
+      <c r="H41" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I41" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J41" s="107"/>
+      <c r="K41" s="107"/>
+      <c r="L41" s="107"/>
+      <c r="M41" s="107"/>
+      <c r="N41" s="107"/>
+      <c r="O41" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P41" s="107"/>
+      <c r="Q41" s="107"/>
+      <c r="R41" s="107"/>
+      <c r="S41" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T41" s="107"/>
+      <c r="U41" s="107"/>
     </row>
     <row r="42" spans="1:21" ht="15">
       <c r="A42">
@@ -20325,32 +20326,32 @@
       <c r="E42" t="s">
         <v>262</v>
       </c>
-      <c r="F42" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G42" s="112"/>
-      <c r="H42" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I42" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J42" s="112"/>
-      <c r="K42" s="112"/>
-      <c r="L42" s="112"/>
-      <c r="M42" s="112"/>
-      <c r="N42" s="112"/>
-      <c r="O42" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P42" s="112"/>
-      <c r="Q42" s="112"/>
-      <c r="R42" s="112"/>
-      <c r="S42" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T42" s="112"/>
-      <c r="U42" s="112"/>
+      <c r="F42" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G42" s="107"/>
+      <c r="H42" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I42" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J42" s="107"/>
+      <c r="K42" s="107"/>
+      <c r="L42" s="107"/>
+      <c r="M42" s="107"/>
+      <c r="N42" s="107"/>
+      <c r="O42" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P42" s="107"/>
+      <c r="Q42" s="107"/>
+      <c r="R42" s="107"/>
+      <c r="S42" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T42" s="107"/>
+      <c r="U42" s="107"/>
     </row>
     <row r="43" spans="1:21" ht="15">
       <c r="A43">
@@ -20368,32 +20369,32 @@
       <c r="E43" t="s">
         <v>262</v>
       </c>
-      <c r="F43" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G43" s="112"/>
-      <c r="H43" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I43" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J43" s="112"/>
-      <c r="K43" s="112"/>
-      <c r="L43" s="112"/>
-      <c r="M43" s="112"/>
-      <c r="N43" s="112"/>
-      <c r="O43" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P43" s="112"/>
-      <c r="Q43" s="112"/>
-      <c r="R43" s="112"/>
-      <c r="S43" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T43" s="112"/>
-      <c r="U43" s="112"/>
+      <c r="F43" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G43" s="107"/>
+      <c r="H43" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I43" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J43" s="107"/>
+      <c r="K43" s="107"/>
+      <c r="L43" s="107"/>
+      <c r="M43" s="107"/>
+      <c r="N43" s="107"/>
+      <c r="O43" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P43" s="107"/>
+      <c r="Q43" s="107"/>
+      <c r="R43" s="107"/>
+      <c r="S43" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T43" s="107"/>
+      <c r="U43" s="107"/>
     </row>
     <row r="44" spans="1:21" ht="15">
       <c r="A44">
@@ -20411,32 +20412,32 @@
       <c r="E44" t="s">
         <v>262</v>
       </c>
-      <c r="F44" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G44" s="112"/>
-      <c r="H44" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I44" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J44" s="112"/>
-      <c r="K44" s="112"/>
-      <c r="L44" s="112"/>
-      <c r="M44" s="112"/>
-      <c r="N44" s="112"/>
-      <c r="O44" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P44" s="112"/>
-      <c r="Q44" s="112"/>
-      <c r="R44" s="112"/>
-      <c r="S44" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T44" s="112"/>
-      <c r="U44" s="112"/>
+      <c r="F44" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G44" s="107"/>
+      <c r="H44" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I44" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J44" s="107"/>
+      <c r="K44" s="107"/>
+      <c r="L44" s="107"/>
+      <c r="M44" s="107"/>
+      <c r="N44" s="107"/>
+      <c r="O44" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P44" s="107"/>
+      <c r="Q44" s="107"/>
+      <c r="R44" s="107"/>
+      <c r="S44" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T44" s="107"/>
+      <c r="U44" s="107"/>
     </row>
     <row r="45" spans="1:21" ht="15">
       <c r="A45">
@@ -20454,36 +20455,36 @@
       <c r="E45" t="s">
         <v>262</v>
       </c>
-      <c r="F45" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G45" s="112"/>
-      <c r="H45" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I45" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J45" s="112"/>
-      <c r="K45" s="112"/>
-      <c r="L45" s="112"/>
-      <c r="M45" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="N45" s="112"/>
-      <c r="O45" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P45" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q45" s="112"/>
-      <c r="R45" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S45" s="112"/>
-      <c r="T45" s="112"/>
-      <c r="U45" s="112" t="s">
+      <c r="F45" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G45" s="107"/>
+      <c r="H45" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I45" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J45" s="107"/>
+      <c r="K45" s="107"/>
+      <c r="L45" s="107"/>
+      <c r="M45" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="N45" s="107"/>
+      <c r="O45" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P45" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q45" s="107"/>
+      <c r="R45" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S45" s="107"/>
+      <c r="T45" s="107"/>
+      <c r="U45" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -20503,32 +20504,32 @@
       <c r="E46" t="s">
         <v>262</v>
       </c>
-      <c r="F46" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G46" s="112"/>
-      <c r="H46" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I46" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J46" s="112"/>
-      <c r="K46" s="112"/>
-      <c r="L46" s="112"/>
-      <c r="M46" s="112"/>
-      <c r="N46" s="112"/>
-      <c r="O46" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P46" s="112"/>
-      <c r="Q46" s="112"/>
-      <c r="R46" s="112"/>
-      <c r="S46" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T46" s="112"/>
-      <c r="U46" s="112" t="s">
+      <c r="F46" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G46" s="107"/>
+      <c r="H46" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I46" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J46" s="107"/>
+      <c r="K46" s="107"/>
+      <c r="L46" s="107"/>
+      <c r="M46" s="107"/>
+      <c r="N46" s="107"/>
+      <c r="O46" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P46" s="107"/>
+      <c r="Q46" s="107"/>
+      <c r="R46" s="107"/>
+      <c r="S46" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T46" s="107"/>
+      <c r="U46" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -20548,32 +20549,32 @@
       <c r="E47" t="s">
         <v>262</v>
       </c>
-      <c r="F47" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G47" s="112"/>
-      <c r="H47" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I47" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J47" s="112"/>
-      <c r="K47" s="112"/>
-      <c r="L47" s="112"/>
-      <c r="M47" s="112"/>
-      <c r="N47" s="112"/>
-      <c r="O47" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P47" s="112"/>
-      <c r="Q47" s="112"/>
-      <c r="R47" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S47" s="112"/>
-      <c r="T47" s="112"/>
-      <c r="U47" s="112"/>
+      <c r="F47" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G47" s="107"/>
+      <c r="H47" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I47" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J47" s="107"/>
+      <c r="K47" s="107"/>
+      <c r="L47" s="107"/>
+      <c r="M47" s="107"/>
+      <c r="N47" s="107"/>
+      <c r="O47" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P47" s="107"/>
+      <c r="Q47" s="107"/>
+      <c r="R47" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S47" s="107"/>
+      <c r="T47" s="107"/>
+      <c r="U47" s="107"/>
     </row>
     <row r="48" spans="1:21" ht="15">
       <c r="A48">
@@ -20591,32 +20592,32 @@
       <c r="E48" t="s">
         <v>262</v>
       </c>
-      <c r="F48" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G48" s="112"/>
-      <c r="H48" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I48" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J48" s="112"/>
-      <c r="K48" s="112"/>
-      <c r="L48" s="112"/>
-      <c r="M48" s="112"/>
-      <c r="N48" s="112"/>
-      <c r="O48" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P48" s="112"/>
-      <c r="Q48" s="112"/>
-      <c r="R48" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S48" s="112"/>
-      <c r="T48" s="112"/>
-      <c r="U48" s="112"/>
+      <c r="F48" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G48" s="107"/>
+      <c r="H48" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I48" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J48" s="107"/>
+      <c r="K48" s="107"/>
+      <c r="L48" s="107"/>
+      <c r="M48" s="107"/>
+      <c r="N48" s="107"/>
+      <c r="O48" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P48" s="107"/>
+      <c r="Q48" s="107"/>
+      <c r="R48" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S48" s="107"/>
+      <c r="T48" s="107"/>
+      <c r="U48" s="107"/>
     </row>
     <row r="49" spans="1:21" ht="15">
       <c r="A49">
@@ -20634,32 +20635,32 @@
       <c r="E49" t="s">
         <v>262</v>
       </c>
-      <c r="F49" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G49" s="112"/>
-      <c r="H49" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I49" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J49" s="112"/>
-      <c r="K49" s="112"/>
-      <c r="L49" s="112"/>
-      <c r="M49" s="112"/>
-      <c r="N49" s="112"/>
-      <c r="O49" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P49" s="112"/>
-      <c r="Q49" s="112"/>
-      <c r="R49" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S49" s="112"/>
-      <c r="T49" s="112"/>
-      <c r="U49" s="112"/>
+      <c r="F49" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G49" s="107"/>
+      <c r="H49" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I49" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J49" s="107"/>
+      <c r="K49" s="107"/>
+      <c r="L49" s="107"/>
+      <c r="M49" s="107"/>
+      <c r="N49" s="107"/>
+      <c r="O49" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P49" s="107"/>
+      <c r="Q49" s="107"/>
+      <c r="R49" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S49" s="107"/>
+      <c r="T49" s="107"/>
+      <c r="U49" s="107"/>
     </row>
     <row r="50" spans="1:21" ht="15">
       <c r="A50">
@@ -20677,32 +20678,32 @@
       <c r="E50" t="s">
         <v>262</v>
       </c>
-      <c r="F50" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G50" s="112"/>
-      <c r="H50" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I50" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J50" s="112"/>
-      <c r="K50" s="112"/>
-      <c r="L50" s="112"/>
-      <c r="M50" s="112"/>
-      <c r="N50" s="112"/>
-      <c r="O50" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P50" s="112"/>
-      <c r="Q50" s="112"/>
-      <c r="R50" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S50" s="112"/>
-      <c r="T50" s="112"/>
-      <c r="U50" s="112"/>
+      <c r="F50" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G50" s="107"/>
+      <c r="H50" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I50" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J50" s="107"/>
+      <c r="K50" s="107"/>
+      <c r="L50" s="107"/>
+      <c r="M50" s="107"/>
+      <c r="N50" s="107"/>
+      <c r="O50" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P50" s="107"/>
+      <c r="Q50" s="107"/>
+      <c r="R50" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S50" s="107"/>
+      <c r="T50" s="107"/>
+      <c r="U50" s="107"/>
     </row>
     <row r="51" spans="1:21" ht="15">
       <c r="A51">
@@ -20720,32 +20721,32 @@
       <c r="E51" t="s">
         <v>262</v>
       </c>
-      <c r="F51" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G51" s="112"/>
-      <c r="H51" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I51" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J51" s="112"/>
-      <c r="K51" s="112"/>
-      <c r="L51" s="112"/>
-      <c r="M51" s="112"/>
-      <c r="N51" s="112"/>
-      <c r="O51" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P51" s="112"/>
-      <c r="Q51" s="112"/>
-      <c r="R51" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S51" s="112"/>
-      <c r="T51" s="112"/>
-      <c r="U51" s="112"/>
+      <c r="F51" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G51" s="107"/>
+      <c r="H51" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I51" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J51" s="107"/>
+      <c r="K51" s="107"/>
+      <c r="L51" s="107"/>
+      <c r="M51" s="107"/>
+      <c r="N51" s="107"/>
+      <c r="O51" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P51" s="107"/>
+      <c r="Q51" s="107"/>
+      <c r="R51" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S51" s="107"/>
+      <c r="T51" s="107"/>
+      <c r="U51" s="107"/>
     </row>
     <row r="52" spans="1:21" ht="15">
       <c r="A52">
@@ -20763,32 +20764,32 @@
       <c r="E52" t="s">
         <v>263</v>
       </c>
-      <c r="F52" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G52" s="112"/>
-      <c r="H52" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I52" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J52" s="112"/>
-      <c r="K52" s="112"/>
-      <c r="L52" s="112"/>
-      <c r="M52" s="112"/>
-      <c r="N52" s="112"/>
-      <c r="O52" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P52" s="112"/>
-      <c r="Q52" s="112"/>
-      <c r="R52" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S52" s="112"/>
-      <c r="T52" s="112"/>
-      <c r="U52" s="112"/>
+      <c r="F52" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G52" s="107"/>
+      <c r="H52" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I52" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J52" s="107"/>
+      <c r="K52" s="107"/>
+      <c r="L52" s="107"/>
+      <c r="M52" s="107"/>
+      <c r="N52" s="107"/>
+      <c r="O52" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P52" s="107"/>
+      <c r="Q52" s="107"/>
+      <c r="R52" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S52" s="107"/>
+      <c r="T52" s="107"/>
+      <c r="U52" s="107"/>
     </row>
     <row r="53" spans="1:21" ht="15">
       <c r="A53">
@@ -20806,32 +20807,32 @@
       <c r="E53" t="s">
         <v>263</v>
       </c>
-      <c r="F53" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G53" s="112"/>
-      <c r="H53" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I53" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J53" s="112"/>
-      <c r="K53" s="112"/>
-      <c r="L53" s="112"/>
-      <c r="M53" s="112"/>
-      <c r="N53" s="112"/>
-      <c r="O53" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P53" s="112"/>
-      <c r="Q53" s="112"/>
-      <c r="R53" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S53" s="112"/>
-      <c r="T53" s="112"/>
-      <c r="U53" s="112"/>
+      <c r="F53" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G53" s="107"/>
+      <c r="H53" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I53" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J53" s="107"/>
+      <c r="K53" s="107"/>
+      <c r="L53" s="107"/>
+      <c r="M53" s="107"/>
+      <c r="N53" s="107"/>
+      <c r="O53" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P53" s="107"/>
+      <c r="Q53" s="107"/>
+      <c r="R53" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S53" s="107"/>
+      <c r="T53" s="107"/>
+      <c r="U53" s="107"/>
     </row>
     <row r="54" spans="1:21" ht="15">
       <c r="A54">
@@ -20849,34 +20850,34 @@
       <c r="E54" t="s">
         <v>263</v>
       </c>
-      <c r="F54" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G54" s="112"/>
-      <c r="H54" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I54" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J54" s="112"/>
-      <c r="K54" s="112"/>
-      <c r="L54" s="112"/>
-      <c r="M54" s="112"/>
-      <c r="N54" s="112"/>
-      <c r="O54" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P54" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q54" s="112"/>
-      <c r="R54" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S54" s="112"/>
-      <c r="T54" s="112"/>
-      <c r="U54" s="112"/>
+      <c r="F54" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G54" s="107"/>
+      <c r="H54" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I54" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J54" s="107"/>
+      <c r="K54" s="107"/>
+      <c r="L54" s="107"/>
+      <c r="M54" s="107"/>
+      <c r="N54" s="107"/>
+      <c r="O54" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P54" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q54" s="107"/>
+      <c r="R54" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S54" s="107"/>
+      <c r="T54" s="107"/>
+      <c r="U54" s="107"/>
     </row>
     <row r="55" spans="1:21" ht="15">
       <c r="A55">
@@ -20894,32 +20895,32 @@
       <c r="E55" t="s">
         <v>263</v>
       </c>
-      <c r="F55" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G55" s="112"/>
-      <c r="H55" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I55" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J55" s="112"/>
-      <c r="K55" s="112"/>
-      <c r="L55" s="112"/>
-      <c r="M55" s="112"/>
-      <c r="N55" s="112"/>
-      <c r="O55" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P55" s="112"/>
-      <c r="Q55" s="112"/>
-      <c r="R55" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S55" s="112"/>
-      <c r="T55" s="112"/>
-      <c r="U55" s="112"/>
+      <c r="F55" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G55" s="107"/>
+      <c r="H55" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I55" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J55" s="107"/>
+      <c r="K55" s="107"/>
+      <c r="L55" s="107"/>
+      <c r="M55" s="107"/>
+      <c r="N55" s="107"/>
+      <c r="O55" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P55" s="107"/>
+      <c r="Q55" s="107"/>
+      <c r="R55" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S55" s="107"/>
+      <c r="T55" s="107"/>
+      <c r="U55" s="107"/>
     </row>
     <row r="56" spans="1:21" ht="15">
       <c r="A56">
@@ -20937,32 +20938,32 @@
       <c r="E56" t="s">
         <v>263</v>
       </c>
-      <c r="F56" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G56" s="112"/>
-      <c r="H56" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I56" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J56" s="112"/>
-      <c r="K56" s="112"/>
-      <c r="L56" s="112"/>
-      <c r="M56" s="112"/>
-      <c r="N56" s="112"/>
-      <c r="O56" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P56" s="112"/>
-      <c r="Q56" s="112"/>
-      <c r="R56" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S56" s="112"/>
-      <c r="T56" s="112"/>
-      <c r="U56" s="112"/>
+      <c r="F56" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G56" s="107"/>
+      <c r="H56" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I56" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J56" s="107"/>
+      <c r="K56" s="107"/>
+      <c r="L56" s="107"/>
+      <c r="M56" s="107"/>
+      <c r="N56" s="107"/>
+      <c r="O56" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P56" s="107"/>
+      <c r="Q56" s="107"/>
+      <c r="R56" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S56" s="107"/>
+      <c r="T56" s="107"/>
+      <c r="U56" s="107"/>
     </row>
     <row r="57" spans="1:21" ht="15">
       <c r="A57">
@@ -20980,32 +20981,32 @@
       <c r="E57" t="s">
         <v>263</v>
       </c>
-      <c r="F57" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G57" s="112"/>
-      <c r="H57" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I57" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J57" s="112"/>
-      <c r="K57" s="112"/>
-      <c r="L57" s="112"/>
-      <c r="M57" s="112"/>
-      <c r="N57" s="112"/>
-      <c r="O57" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P57" s="112"/>
-      <c r="Q57" s="112"/>
-      <c r="R57" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S57" s="112"/>
-      <c r="T57" s="112"/>
-      <c r="U57" s="112"/>
+      <c r="F57" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G57" s="107"/>
+      <c r="H57" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I57" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J57" s="107"/>
+      <c r="K57" s="107"/>
+      <c r="L57" s="107"/>
+      <c r="M57" s="107"/>
+      <c r="N57" s="107"/>
+      <c r="O57" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P57" s="107"/>
+      <c r="Q57" s="107"/>
+      <c r="R57" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S57" s="107"/>
+      <c r="T57" s="107"/>
+      <c r="U57" s="107"/>
     </row>
     <row r="58" spans="1:21" ht="15">
       <c r="A58">
@@ -21023,34 +21024,34 @@
       <c r="E58" t="s">
         <v>263</v>
       </c>
-      <c r="F58" s="112"/>
-      <c r="G58" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="H58" s="112"/>
-      <c r="I58" s="112"/>
-      <c r="J58" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="K58" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="L58" s="112"/>
-      <c r="M58" s="112"/>
-      <c r="N58" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="O58" s="112"/>
-      <c r="P58" s="112"/>
-      <c r="Q58" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="R58" s="112"/>
-      <c r="S58" s="112"/>
-      <c r="T58" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="U58" s="112"/>
+      <c r="F58" s="107"/>
+      <c r="G58" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="H58" s="107"/>
+      <c r="I58" s="107"/>
+      <c r="J58" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="K58" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="L58" s="107"/>
+      <c r="M58" s="107"/>
+      <c r="N58" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="O58" s="107"/>
+      <c r="P58" s="107"/>
+      <c r="Q58" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="R58" s="107"/>
+      <c r="S58" s="107"/>
+      <c r="T58" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="U58" s="107"/>
     </row>
     <row r="59" spans="1:21" ht="15">
       <c r="A59">
@@ -21068,32 +21069,32 @@
       <c r="E59" t="s">
         <v>263</v>
       </c>
-      <c r="F59" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G59" s="112"/>
-      <c r="H59" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I59" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J59" s="112"/>
-      <c r="K59" s="112"/>
-      <c r="L59" s="112"/>
-      <c r="M59" s="112"/>
-      <c r="N59" s="112"/>
-      <c r="O59" s="112"/>
-      <c r="P59" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="Q59" s="112"/>
-      <c r="R59" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S59" s="112"/>
-      <c r="T59" s="112"/>
-      <c r="U59" s="112"/>
+      <c r="F59" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G59" s="107"/>
+      <c r="H59" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I59" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J59" s="107"/>
+      <c r="K59" s="107"/>
+      <c r="L59" s="107"/>
+      <c r="M59" s="107"/>
+      <c r="N59" s="107"/>
+      <c r="O59" s="107"/>
+      <c r="P59" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q59" s="107"/>
+      <c r="R59" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S59" s="107"/>
+      <c r="T59" s="107"/>
+      <c r="U59" s="107"/>
     </row>
     <row r="60" spans="1:21" ht="15">
       <c r="A60" t="s">
@@ -21107,22 +21108,22 @@
       </c>
       <c r="D60"/>
       <c r="E60"/>
-      <c r="F60" s="112"/>
-      <c r="G60" s="112"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
-      <c r="J60" s="112"/>
-      <c r="K60" s="112"/>
-      <c r="L60" s="112"/>
-      <c r="M60" s="112"/>
-      <c r="N60" s="112"/>
-      <c r="O60" s="112"/>
-      <c r="P60" s="112"/>
-      <c r="Q60" s="112"/>
-      <c r="R60" s="112"/>
-      <c r="S60" s="112"/>
-      <c r="T60" s="112"/>
-      <c r="U60" s="112"/>
+      <c r="F60" s="107"/>
+      <c r="G60" s="107"/>
+      <c r="H60" s="107"/>
+      <c r="I60" s="107"/>
+      <c r="J60" s="107"/>
+      <c r="K60" s="107"/>
+      <c r="L60" s="107"/>
+      <c r="M60" s="107"/>
+      <c r="N60" s="107"/>
+      <c r="O60" s="107"/>
+      <c r="P60" s="107"/>
+      <c r="Q60" s="107"/>
+      <c r="R60" s="107"/>
+      <c r="S60" s="107"/>
+      <c r="T60" s="107"/>
+      <c r="U60" s="107"/>
     </row>
     <row r="61" spans="1:21" ht="15">
       <c r="A61">
@@ -21140,32 +21141,32 @@
       <c r="E61" t="s">
         <v>264</v>
       </c>
-      <c r="F61" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G61" s="112"/>
-      <c r="H61" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I61" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J61" s="112"/>
-      <c r="K61" s="112"/>
-      <c r="L61" s="112"/>
-      <c r="M61" s="112"/>
-      <c r="N61" s="112"/>
-      <c r="O61" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P61" s="112"/>
-      <c r="Q61" s="112"/>
-      <c r="R61" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S61" s="112"/>
-      <c r="T61" s="112"/>
-      <c r="U61" s="112"/>
+      <c r="F61" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G61" s="107"/>
+      <c r="H61" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I61" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J61" s="107"/>
+      <c r="K61" s="107"/>
+      <c r="L61" s="107"/>
+      <c r="M61" s="107"/>
+      <c r="N61" s="107"/>
+      <c r="O61" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P61" s="107"/>
+      <c r="Q61" s="107"/>
+      <c r="R61" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S61" s="107"/>
+      <c r="T61" s="107"/>
+      <c r="U61" s="107"/>
     </row>
     <row r="62" spans="1:21" ht="15">
       <c r="A62">
@@ -21183,32 +21184,32 @@
       <c r="E62" t="s">
         <v>262</v>
       </c>
-      <c r="F62" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G62" s="112"/>
-      <c r="H62" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I62" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J62" s="112"/>
-      <c r="K62" s="112"/>
-      <c r="L62" s="112"/>
-      <c r="M62" s="112"/>
-      <c r="N62" s="112"/>
-      <c r="O62" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P62" s="112"/>
-      <c r="Q62" s="112"/>
-      <c r="R62" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="S62" s="112"/>
-      <c r="T62" s="112"/>
-      <c r="U62" s="112" t="s">
+      <c r="F62" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G62" s="107"/>
+      <c r="H62" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I62" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J62" s="107"/>
+      <c r="K62" s="107"/>
+      <c r="L62" s="107"/>
+      <c r="M62" s="107"/>
+      <c r="N62" s="107"/>
+      <c r="O62" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P62" s="107"/>
+      <c r="Q62" s="107"/>
+      <c r="R62" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="S62" s="107"/>
+      <c r="T62" s="107"/>
+      <c r="U62" s="107" t="s">
         <v>840</v>
       </c>
     </row>
@@ -21228,32 +21229,32 @@
       <c r="E63" t="s">
         <v>262</v>
       </c>
-      <c r="F63" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G63" s="112"/>
-      <c r="H63" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I63" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J63" s="112"/>
-      <c r="K63" s="112"/>
-      <c r="L63" s="112"/>
-      <c r="M63" s="112"/>
-      <c r="N63" s="112"/>
-      <c r="O63" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P63" s="112"/>
-      <c r="Q63" s="112"/>
-      <c r="R63" s="112"/>
-      <c r="S63" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T63" s="112"/>
-      <c r="U63" s="112"/>
+      <c r="F63" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G63" s="107"/>
+      <c r="H63" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I63" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J63" s="107"/>
+      <c r="K63" s="107"/>
+      <c r="L63" s="107"/>
+      <c r="M63" s="107"/>
+      <c r="N63" s="107"/>
+      <c r="O63" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P63" s="107"/>
+      <c r="Q63" s="107"/>
+      <c r="R63" s="107"/>
+      <c r="S63" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T63" s="107"/>
+      <c r="U63" s="107"/>
     </row>
     <row r="64" spans="1:21" ht="15">
       <c r="A64">
@@ -21271,32 +21272,32 @@
       <c r="E64" t="s">
         <v>262</v>
       </c>
-      <c r="F64" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G64" s="112"/>
-      <c r="H64" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I64" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J64" s="112"/>
-      <c r="K64" s="112"/>
-      <c r="L64" s="112"/>
-      <c r="M64" s="112"/>
-      <c r="N64" s="112"/>
-      <c r="O64" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P64" s="112"/>
-      <c r="Q64" s="112"/>
-      <c r="R64" s="112"/>
-      <c r="S64" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T64" s="112"/>
-      <c r="U64" s="112"/>
+      <c r="F64" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G64" s="107"/>
+      <c r="H64" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I64" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J64" s="107"/>
+      <c r="K64" s="107"/>
+      <c r="L64" s="107"/>
+      <c r="M64" s="107"/>
+      <c r="N64" s="107"/>
+      <c r="O64" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P64" s="107"/>
+      <c r="Q64" s="107"/>
+      <c r="R64" s="107"/>
+      <c r="S64" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T64" s="107"/>
+      <c r="U64" s="107"/>
     </row>
     <row r="65" spans="1:21" ht="15">
       <c r="A65">
@@ -21314,32 +21315,32 @@
       <c r="E65" t="s">
         <v>262</v>
       </c>
-      <c r="F65" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G65" s="112"/>
-      <c r="H65" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I65" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J65" s="112"/>
-      <c r="K65" s="112"/>
-      <c r="L65" s="112"/>
-      <c r="M65" s="112"/>
-      <c r="N65" s="112"/>
-      <c r="O65" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P65" s="112"/>
-      <c r="Q65" s="112"/>
-      <c r="R65" s="112"/>
-      <c r="S65" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T65" s="112"/>
-      <c r="U65" s="112"/>
+      <c r="F65" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G65" s="107"/>
+      <c r="H65" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I65" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J65" s="107"/>
+      <c r="K65" s="107"/>
+      <c r="L65" s="107"/>
+      <c r="M65" s="107"/>
+      <c r="N65" s="107"/>
+      <c r="O65" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P65" s="107"/>
+      <c r="Q65" s="107"/>
+      <c r="R65" s="107"/>
+      <c r="S65" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T65" s="107"/>
+      <c r="U65" s="107"/>
     </row>
     <row r="66" spans="1:21" ht="15">
       <c r="A66">
@@ -21357,32 +21358,32 @@
       <c r="E66" t="s">
         <v>262</v>
       </c>
-      <c r="F66" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="G66" s="112"/>
-      <c r="H66" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="I66" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="J66" s="112"/>
-      <c r="K66" s="112"/>
-      <c r="L66" s="112"/>
-      <c r="M66" s="112"/>
-      <c r="N66" s="112"/>
-      <c r="O66" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="P66" s="112"/>
-      <c r="Q66" s="112"/>
-      <c r="R66" s="112"/>
-      <c r="S66" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="T66" s="112"/>
-      <c r="U66" s="112"/>
+      <c r="F66" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="G66" s="107"/>
+      <c r="H66" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="I66" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="J66" s="107"/>
+      <c r="K66" s="107"/>
+      <c r="L66" s="107"/>
+      <c r="M66" s="107"/>
+      <c r="N66" s="107"/>
+      <c r="O66" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="P66" s="107"/>
+      <c r="Q66" s="107"/>
+      <c r="R66" s="107"/>
+      <c r="S66" s="107" t="s">
+        <v>840</v>
+      </c>
+      <c r="T66" s="107"/>
+      <c r="U66" s="107"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K479" xr:uid="{5E4D3AFA-EEF7-4320-87DA-2CF2F0B83EA8}"/>
@@ -21397,7 +21398,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:Q452"/>
+  <dimension ref="A1:Q453"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="2" customWidth="1"/>
@@ -23018,28 +23019,28 @@
       <c r="A406" s="2">
         <v>5</v>
       </c>
-      <c r="B406" s="105" t="s">
+      <c r="B406" s="104" t="s">
         <v>133</v>
       </c>
       <c r="C406" s="59"/>
       <c r="D406" s="59"/>
     </row>
     <row r="407" spans="1:12" ht="15">
-      <c r="B407" s="106" t="s">
+      <c r="B407" s="105" t="s">
         <v>134</v>
       </c>
       <c r="C407" s="59"/>
       <c r="D407" s="59"/>
     </row>
     <row r="408" spans="1:12" ht="18.75">
-      <c r="B408" s="106" t="s">
+      <c r="B408" s="105" t="s">
         <v>135</v>
       </c>
       <c r="C408" s="59"/>
       <c r="D408" s="59"/>
     </row>
     <row r="409" spans="1:12" ht="15">
-      <c r="B409" s="107" t="s">
+      <c r="B409" s="106" t="s">
         <v>136</v>
       </c>
       <c r="C409" s="59"/>
@@ -23052,582 +23053,596 @@
       <c r="B411" s="103"/>
     </row>
     <row r="412" spans="1:12" ht="15">
-      <c r="A412" s="113">
+      <c r="A412" s="108">
         <v>6</v>
       </c>
-      <c r="B412" s="113" t="s">
+      <c r="B412" s="108" t="s">
         <v>137</v>
       </c>
-      <c r="C412" s="114"/>
-      <c r="D412" s="114"/>
-      <c r="E412" s="115"/>
-      <c r="F412" s="115"/>
-      <c r="G412" s="115"/>
-      <c r="H412" s="115"/>
-      <c r="I412" s="115"/>
-      <c r="J412" s="115"/>
-      <c r="K412" s="115"/>
-      <c r="L412" s="115"/>
+      <c r="C412" s="109"/>
+      <c r="D412" s="109"/>
+      <c r="E412" s="110"/>
+      <c r="F412" s="110"/>
+      <c r="G412" s="110"/>
+      <c r="H412" s="110"/>
+      <c r="I412" s="110"/>
+      <c r="J412" s="110"/>
+      <c r="K412" s="110"/>
+      <c r="L412" s="110"/>
     </row>
     <row r="413" spans="1:12" ht="15">
-      <c r="A413" s="115"/>
-      <c r="B413" s="116" t="s">
+      <c r="A413" s="110"/>
+      <c r="B413" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="C413" s="115"/>
-      <c r="D413" s="115"/>
-      <c r="E413" s="115"/>
-      <c r="F413" s="115"/>
-      <c r="G413" s="115"/>
-      <c r="H413" s="115"/>
-      <c r="I413" s="115"/>
-      <c r="J413" s="115"/>
-      <c r="K413" s="115"/>
-      <c r="L413" s="115"/>
+      <c r="C413" s="110"/>
+      <c r="D413" s="110"/>
+      <c r="E413" s="110"/>
+      <c r="F413" s="110"/>
+      <c r="G413" s="110"/>
+      <c r="H413" s="110"/>
+      <c r="I413" s="110"/>
+      <c r="J413" s="110"/>
+      <c r="K413" s="110"/>
+      <c r="L413" s="110"/>
     </row>
     <row r="414" spans="1:12" ht="15">
-      <c r="A414" s="115"/>
-      <c r="B414" s="115" t="s">
+      <c r="A414" s="110"/>
+      <c r="B414" s="110" t="s">
         <v>138</v>
       </c>
-      <c r="C414" s="117"/>
-      <c r="D414" s="117"/>
-      <c r="E414" s="117"/>
-      <c r="F414" s="115"/>
-      <c r="G414" s="115"/>
-      <c r="H414" s="115"/>
-      <c r="I414" s="115"/>
-      <c r="J414" s="115"/>
-      <c r="K414" s="115"/>
-      <c r="L414" s="115"/>
+      <c r="C414" s="112"/>
+      <c r="D414" s="112"/>
+      <c r="E414" s="112"/>
+      <c r="F414" s="110"/>
+      <c r="G414" s="110"/>
+      <c r="H414" s="110"/>
+      <c r="I414" s="110"/>
+      <c r="J414" s="110"/>
+      <c r="K414" s="110"/>
+      <c r="L414" s="110"/>
     </row>
     <row r="415" spans="1:12" ht="15">
-      <c r="A415" s="115"/>
-      <c r="B415" s="115" t="s">
+      <c r="A415" s="110"/>
+      <c r="B415" s="110" t="s">
         <v>139</v>
       </c>
-      <c r="C415" s="117"/>
-      <c r="D415" s="115"/>
-      <c r="E415" s="115"/>
-      <c r="F415" s="115"/>
-      <c r="G415" s="115"/>
-      <c r="H415" s="115"/>
-      <c r="I415" s="115"/>
-      <c r="J415" s="115"/>
-      <c r="K415" s="115"/>
-      <c r="L415" s="115"/>
+      <c r="C415" s="112"/>
+      <c r="D415" s="110"/>
+      <c r="E415" s="110"/>
+      <c r="F415" s="110"/>
+      <c r="G415" s="110"/>
+      <c r="H415" s="110"/>
+      <c r="I415" s="110"/>
+      <c r="J415" s="110"/>
+      <c r="K415" s="110"/>
+      <c r="L415" s="110"/>
     </row>
     <row r="416" spans="1:12" ht="15">
-      <c r="A416" s="115"/>
-      <c r="B416" s="115" t="s">
+      <c r="A416" s="110"/>
+      <c r="B416" s="110" t="s">
         <v>140</v>
       </c>
-      <c r="C416" s="117"/>
-      <c r="D416" s="117"/>
-      <c r="E416" s="117"/>
-      <c r="F416" s="117"/>
-      <c r="G416" s="115"/>
-      <c r="H416" s="115"/>
-      <c r="I416" s="115"/>
-      <c r="J416" s="115"/>
-      <c r="K416" s="115"/>
-      <c r="L416" s="115"/>
+      <c r="C416" s="112"/>
+      <c r="D416" s="112"/>
+      <c r="E416" s="112"/>
+      <c r="F416" s="112"/>
+      <c r="G416" s="110"/>
+      <c r="H416" s="110"/>
+      <c r="I416" s="110"/>
+      <c r="J416" s="110"/>
+      <c r="K416" s="110"/>
+      <c r="L416" s="110"/>
     </row>
     <row r="417" spans="1:12" ht="15">
-      <c r="A417" s="115"/>
-      <c r="B417" s="115" t="s">
+      <c r="A417" s="110"/>
+      <c r="B417" s="110" t="s">
         <v>141</v>
       </c>
-      <c r="C417" s="117"/>
-      <c r="D417" s="117"/>
-      <c r="E417" s="117"/>
-      <c r="F417" s="115"/>
-      <c r="G417" s="115"/>
-      <c r="H417" s="115"/>
-      <c r="I417" s="115"/>
-      <c r="J417" s="115"/>
-      <c r="K417" s="115"/>
-      <c r="L417" s="115"/>
+      <c r="C417" s="112"/>
+      <c r="D417" s="112"/>
+      <c r="E417" s="112"/>
+      <c r="F417" s="110"/>
+      <c r="G417" s="110"/>
+      <c r="H417" s="110"/>
+      <c r="I417" s="110"/>
+      <c r="J417" s="110"/>
+      <c r="K417" s="110"/>
+      <c r="L417" s="110"/>
     </row>
     <row r="418" spans="1:12" ht="15">
-      <c r="A418" s="115"/>
-      <c r="B418" s="115" t="s">
+      <c r="A418" s="110"/>
+      <c r="B418" s="110" t="s">
         <v>142</v>
       </c>
-      <c r="C418" s="117"/>
-      <c r="D418" s="117"/>
-      <c r="E418" s="117"/>
-      <c r="F418" s="115"/>
-      <c r="G418" s="115"/>
-      <c r="H418" s="115"/>
-      <c r="I418" s="115"/>
-      <c r="J418" s="115"/>
-      <c r="K418" s="115"/>
-      <c r="L418" s="115"/>
+      <c r="C418" s="112"/>
+      <c r="D418" s="112"/>
+      <c r="E418" s="112"/>
+      <c r="F418" s="110"/>
+      <c r="G418" s="110"/>
+      <c r="H418" s="110"/>
+      <c r="I418" s="110"/>
+      <c r="J418" s="110"/>
+      <c r="K418" s="110"/>
+      <c r="L418" s="110"/>
     </row>
     <row r="419" spans="1:12" ht="15">
-      <c r="A419" s="115"/>
-      <c r="B419" s="115"/>
-      <c r="C419" s="115"/>
-      <c r="D419" s="115"/>
-      <c r="E419" s="115"/>
-      <c r="F419" s="115"/>
-      <c r="G419" s="115"/>
-      <c r="H419" s="115"/>
-      <c r="I419" s="115"/>
-      <c r="J419" s="115"/>
-      <c r="K419" s="115"/>
-      <c r="L419" s="115"/>
+      <c r="A419" s="110"/>
+      <c r="B419" s="110"/>
+      <c r="C419" s="110"/>
+      <c r="D419" s="110"/>
+      <c r="E419" s="110"/>
+      <c r="F419" s="110"/>
+      <c r="G419" s="110"/>
+      <c r="H419" s="110"/>
+      <c r="I419" s="110"/>
+      <c r="J419" s="110"/>
+      <c r="K419" s="110"/>
+      <c r="L419" s="110"/>
     </row>
     <row r="420" spans="1:12" ht="15">
-      <c r="A420" s="115"/>
-      <c r="B420" s="118" t="s">
+      <c r="A420" s="110"/>
+      <c r="B420" s="113" t="s">
         <v>143</v>
       </c>
-      <c r="C420" s="119"/>
-      <c r="D420" s="115"/>
-      <c r="E420" s="115"/>
-      <c r="F420" s="115"/>
-      <c r="G420" s="115"/>
-      <c r="H420" s="115"/>
-      <c r="I420" s="115"/>
-      <c r="J420" s="115"/>
-      <c r="K420" s="115"/>
-      <c r="L420" s="115"/>
+      <c r="C420" s="114"/>
+      <c r="D420" s="110"/>
+      <c r="E420" s="110"/>
+      <c r="F420" s="110"/>
+      <c r="G420" s="110"/>
+      <c r="H420" s="110"/>
+      <c r="I420" s="110"/>
+      <c r="J420" s="110"/>
+      <c r="K420" s="110"/>
+      <c r="L420" s="110"/>
     </row>
     <row r="421" spans="1:12" ht="15">
-      <c r="A421" s="115"/>
-      <c r="B421" s="115" t="s">
+      <c r="A421" s="110"/>
+      <c r="B421" s="110" t="s">
         <v>144</v>
       </c>
-      <c r="C421" s="117"/>
-      <c r="D421" s="117"/>
-      <c r="E421" s="117"/>
-      <c r="F421" s="117"/>
-      <c r="G421" s="117"/>
-      <c r="H421" s="115" t="s">
+      <c r="C421" s="112"/>
+      <c r="D421" s="112"/>
+      <c r="E421" s="112"/>
+      <c r="F421" s="112"/>
+      <c r="G421" s="112"/>
+      <c r="H421" s="110" t="s">
         <v>145</v>
       </c>
-      <c r="I421" s="117"/>
-      <c r="J421" s="117"/>
-      <c r="K421" s="117"/>
-      <c r="L421" s="117"/>
+      <c r="I421" s="112"/>
+      <c r="J421" s="112"/>
+      <c r="K421" s="112"/>
+      <c r="L421" s="112"/>
     </row>
     <row r="422" spans="1:12" ht="15">
-      <c r="A422" s="115"/>
-      <c r="B422" s="120" t="s">
+      <c r="A422" s="110"/>
+      <c r="B422" s="115" t="s">
         <v>146</v>
       </c>
-      <c r="C422" s="121"/>
-      <c r="D422" s="121"/>
-      <c r="E422" s="115"/>
-      <c r="F422" s="115"/>
-      <c r="G422" s="115"/>
-      <c r="H422" s="120" t="s">
+      <c r="C422" s="116"/>
+      <c r="D422" s="116"/>
+      <c r="E422" s="110"/>
+      <c r="F422" s="110"/>
+      <c r="G422" s="110"/>
+      <c r="H422" s="115" t="s">
         <v>147</v>
       </c>
-      <c r="I422" s="121"/>
-      <c r="J422" s="121"/>
-      <c r="K422" s="121"/>
-      <c r="L422" s="115"/>
+      <c r="I422" s="116"/>
+      <c r="J422" s="116"/>
+      <c r="K422" s="116"/>
+      <c r="L422" s="110"/>
     </row>
     <row r="423" spans="1:12" ht="15">
-      <c r="A423" s="115"/>
-      <c r="B423" s="115"/>
-      <c r="C423" s="115"/>
-      <c r="D423" s="115"/>
-      <c r="E423" s="115"/>
-      <c r="F423" s="115"/>
-      <c r="G423" s="115"/>
-      <c r="H423" s="115"/>
-      <c r="I423" s="115"/>
-      <c r="J423" s="115"/>
-      <c r="K423" s="115"/>
-      <c r="L423" s="115"/>
+      <c r="A423" s="110"/>
+      <c r="B423" s="110"/>
+      <c r="C423" s="110"/>
+      <c r="D423" s="110"/>
+      <c r="E423" s="110"/>
+      <c r="F423" s="110"/>
+      <c r="G423" s="110"/>
+      <c r="H423" s="110"/>
+      <c r="I423" s="110"/>
+      <c r="J423" s="110"/>
+      <c r="K423" s="110"/>
+      <c r="L423" s="110"/>
     </row>
     <row r="424" spans="1:12" ht="15">
-      <c r="A424" s="115"/>
-      <c r="B424" s="115" t="s">
+      <c r="A424" s="110"/>
+      <c r="B424" s="110" t="s">
         <v>148</v>
       </c>
-      <c r="C424" s="117"/>
-      <c r="D424" s="117"/>
-      <c r="E424" s="115"/>
-      <c r="F424" s="115"/>
-      <c r="G424" s="115"/>
-      <c r="H424" s="115"/>
-      <c r="I424" s="115"/>
-      <c r="J424" s="115"/>
-      <c r="K424" s="115"/>
-      <c r="L424" s="115"/>
+      <c r="C424" s="112"/>
+      <c r="D424" s="112"/>
+      <c r="E424" s="110"/>
+      <c r="F424" s="110"/>
+      <c r="G424" s="110"/>
+      <c r="H424" s="110"/>
+      <c r="I424" s="110"/>
+      <c r="J424" s="110"/>
+      <c r="K424" s="110"/>
+      <c r="L424" s="110"/>
     </row>
     <row r="425" spans="1:12" ht="15">
-      <c r="A425" s="115"/>
-      <c r="B425" s="115"/>
-      <c r="C425" s="117"/>
-      <c r="D425" s="117"/>
-      <c r="E425" s="115"/>
-      <c r="F425" s="115"/>
-      <c r="G425" s="115"/>
-      <c r="H425" s="115"/>
-      <c r="I425" s="115"/>
-      <c r="J425" s="115"/>
-      <c r="K425" s="115"/>
-      <c r="L425" s="115"/>
+      <c r="A425" s="110"/>
+      <c r="B425" s="110"/>
+      <c r="C425" s="112"/>
+      <c r="D425" s="112"/>
+      <c r="E425" s="110"/>
+      <c r="F425" s="110"/>
+      <c r="G425" s="110"/>
+      <c r="H425" s="110"/>
+      <c r="I425" s="110"/>
+      <c r="J425" s="110"/>
+      <c r="K425" s="110"/>
+      <c r="L425" s="110"/>
     </row>
     <row r="426" spans="1:12" ht="15">
-      <c r="A426" s="115"/>
-      <c r="B426" s="115" t="s">
+      <c r="A426" s="110"/>
+      <c r="B426" s="110" t="s">
         <v>149</v>
       </c>
-      <c r="C426" s="117"/>
-      <c r="D426" s="117"/>
-      <c r="E426" s="115"/>
-      <c r="F426" s="115"/>
-      <c r="G426" s="115"/>
-      <c r="H426" s="115"/>
-      <c r="I426" s="115"/>
-      <c r="J426" s="115"/>
-      <c r="K426" s="115"/>
-      <c r="L426" s="115"/>
+      <c r="C426" s="112"/>
+      <c r="D426" s="112"/>
+      <c r="E426" s="110"/>
+      <c r="F426" s="110"/>
+      <c r="G426" s="110"/>
+      <c r="H426" s="110"/>
+      <c r="I426" s="110"/>
+      <c r="J426" s="110"/>
+      <c r="K426" s="110"/>
+      <c r="L426" s="110"/>
     </row>
     <row r="427" spans="1:12" ht="15">
-      <c r="A427" s="115"/>
-      <c r="B427" s="115"/>
-      <c r="C427" s="115" t="s">
+      <c r="A427" s="110"/>
+      <c r="B427" s="110"/>
+      <c r="C427" s="120" t="s">
         <v>150</v>
       </c>
-      <c r="D427" s="117"/>
-      <c r="E427" s="115"/>
-      <c r="F427" s="115"/>
-      <c r="G427" s="115"/>
-      <c r="H427" s="115"/>
-      <c r="I427" s="115"/>
-      <c r="J427" s="115"/>
-      <c r="K427" s="115"/>
-      <c r="L427" s="115"/>
+      <c r="D427" s="112"/>
+      <c r="E427" s="110"/>
+      <c r="F427" s="110"/>
+      <c r="G427" s="110"/>
+      <c r="H427" s="110"/>
+      <c r="I427" s="110"/>
+      <c r="J427" s="110"/>
+      <c r="K427" s="110"/>
+      <c r="L427" s="110"/>
     </row>
     <row r="428" spans="1:12" ht="15">
-      <c r="A428" s="115"/>
-      <c r="B428" s="115"/>
-      <c r="C428" s="120" t="s">
+      <c r="A428" s="110"/>
+      <c r="B428" s="110"/>
+      <c r="C428" s="115" t="s">
         <v>151</v>
       </c>
-      <c r="D428" s="121"/>
-      <c r="E428" s="121"/>
-      <c r="F428" s="115"/>
-      <c r="G428" s="115"/>
-      <c r="H428" s="115"/>
-      <c r="I428" s="115"/>
-      <c r="J428" s="115"/>
-      <c r="K428" s="115"/>
-      <c r="L428" s="115"/>
+      <c r="D428" s="116"/>
+      <c r="E428" s="116"/>
+      <c r="F428" s="110"/>
+      <c r="G428" s="110"/>
+      <c r="H428" s="110"/>
+      <c r="I428" s="110"/>
+      <c r="J428" s="110"/>
+      <c r="K428" s="110"/>
+      <c r="L428" s="110"/>
     </row>
     <row r="429" spans="1:12" ht="15">
-      <c r="A429" s="115"/>
-      <c r="B429" s="115"/>
-      <c r="C429" s="120"/>
-      <c r="D429" s="121"/>
-      <c r="E429" s="121"/>
-      <c r="F429" s="115"/>
-      <c r="G429" s="115"/>
-      <c r="H429" s="115"/>
-      <c r="I429" s="115"/>
-      <c r="J429" s="115"/>
-      <c r="K429" s="115"/>
-      <c r="L429" s="115"/>
+      <c r="A429" s="110"/>
+      <c r="B429" s="110"/>
+      <c r="C429" s="115"/>
+      <c r="D429" s="116"/>
+      <c r="E429" s="116"/>
+      <c r="F429" s="110"/>
+      <c r="G429" s="110"/>
+      <c r="H429" s="110"/>
+      <c r="I429" s="110"/>
+      <c r="J429" s="110"/>
+      <c r="K429" s="110"/>
+      <c r="L429" s="110"/>
     </row>
     <row r="430" spans="1:12" ht="15">
-      <c r="A430" s="115"/>
-      <c r="B430" s="115" t="s">
+      <c r="A430" s="110"/>
+      <c r="B430" s="110" t="s">
         <v>152</v>
       </c>
-      <c r="C430" s="117"/>
-      <c r="D430" s="117"/>
-      <c r="E430" s="115"/>
-      <c r="F430" s="115"/>
-      <c r="G430" s="115"/>
-      <c r="H430" s="115"/>
-      <c r="I430" s="115"/>
-      <c r="J430" s="115"/>
-      <c r="K430" s="115"/>
-      <c r="L430" s="115"/>
+      <c r="C430" s="112"/>
+      <c r="D430" s="112"/>
+      <c r="E430" s="110"/>
+      <c r="F430" s="110"/>
+      <c r="G430" s="110"/>
+      <c r="H430" s="110"/>
+      <c r="I430" s="110"/>
+      <c r="J430" s="110"/>
+      <c r="K430" s="110"/>
+      <c r="L430" s="110"/>
     </row>
     <row r="431" spans="1:12" ht="15">
-      <c r="A431" s="115"/>
-      <c r="B431" s="115"/>
-      <c r="C431" s="115" t="s">
+      <c r="A431" s="110"/>
+      <c r="B431" s="110"/>
+      <c r="C431" s="110" t="s">
         <v>153</v>
       </c>
-      <c r="D431" s="117"/>
-      <c r="E431" s="115"/>
-      <c r="F431" s="115"/>
-      <c r="G431" s="115"/>
-      <c r="H431" s="115"/>
-      <c r="I431" s="115"/>
-      <c r="J431" s="115"/>
-      <c r="K431" s="115"/>
-      <c r="L431" s="115"/>
+      <c r="D431" s="112"/>
+      <c r="E431" s="110"/>
+      <c r="F431" s="110"/>
+      <c r="G431" s="110"/>
+      <c r="H431" s="110"/>
+      <c r="I431" s="110"/>
+      <c r="J431" s="110"/>
+      <c r="K431" s="110"/>
+      <c r="L431" s="110"/>
     </row>
     <row r="432" spans="1:12" ht="15">
-      <c r="A432" s="115"/>
-      <c r="B432" s="115"/>
-      <c r="C432" s="120" t="s">
+      <c r="A432" s="110"/>
+      <c r="B432" s="110"/>
+      <c r="C432" s="115" t="s">
         <v>154</v>
       </c>
-      <c r="D432" s="121"/>
-      <c r="E432" s="121"/>
-      <c r="F432" s="115"/>
-      <c r="G432" s="115"/>
-      <c r="H432" s="115"/>
-      <c r="I432" s="115"/>
-      <c r="J432" s="115"/>
-      <c r="K432" s="115"/>
-      <c r="L432" s="115"/>
+      <c r="D432" s="116"/>
+      <c r="E432" s="116"/>
+      <c r="F432" s="110"/>
+      <c r="G432" s="110"/>
+      <c r="H432" s="110"/>
+      <c r="I432" s="110"/>
+      <c r="J432" s="110"/>
+      <c r="K432" s="110"/>
+      <c r="L432" s="110"/>
     </row>
     <row r="433" spans="1:12" ht="15">
-      <c r="A433" s="115"/>
-      <c r="B433" s="115"/>
-      <c r="C433" s="120"/>
-      <c r="D433" s="121"/>
-      <c r="E433" s="121"/>
-      <c r="F433" s="115"/>
-      <c r="G433" s="115"/>
-      <c r="H433" s="115"/>
-      <c r="I433" s="115"/>
-      <c r="J433" s="115"/>
-      <c r="K433" s="115"/>
-      <c r="L433" s="115"/>
+      <c r="A433" s="110"/>
+      <c r="B433" s="110"/>
+      <c r="C433" s="115"/>
+      <c r="D433" s="116"/>
+      <c r="E433" s="116"/>
+      <c r="F433" s="110"/>
+      <c r="G433" s="110"/>
+      <c r="H433" s="110"/>
+      <c r="I433" s="110"/>
+      <c r="J433" s="110"/>
+      <c r="K433" s="110"/>
+      <c r="L433" s="110"/>
     </row>
     <row r="434" spans="1:12" ht="15">
-      <c r="A434" s="115"/>
-      <c r="B434" s="115" t="s">
+      <c r="A434" s="110"/>
+      <c r="B434" s="110" t="s">
         <v>155</v>
       </c>
-      <c r="C434" s="117"/>
-      <c r="D434" s="117"/>
-      <c r="E434" s="117"/>
-      <c r="F434" s="115"/>
-      <c r="G434" s="115"/>
-      <c r="H434" s="115"/>
-      <c r="I434" s="115"/>
-      <c r="J434" s="115"/>
-      <c r="K434" s="115"/>
-      <c r="L434" s="115"/>
+      <c r="C434" s="112"/>
+      <c r="D434" s="112"/>
+      <c r="E434" s="112"/>
+      <c r="F434" s="110"/>
+      <c r="G434" s="110"/>
+      <c r="H434" s="110"/>
+      <c r="I434" s="110"/>
+      <c r="J434" s="110"/>
+      <c r="K434" s="110"/>
+      <c r="L434" s="110"/>
     </row>
     <row r="435" spans="1:12" ht="15">
-      <c r="A435" s="115"/>
-      <c r="B435" s="115"/>
-      <c r="C435" s="115" t="s">
+      <c r="A435" s="110"/>
+      <c r="B435" s="110"/>
+      <c r="C435" s="120" t="s">
         <v>156</v>
       </c>
-      <c r="D435" s="117"/>
-      <c r="E435" s="117"/>
-      <c r="F435" s="115"/>
-      <c r="G435" s="115"/>
-      <c r="H435" s="115"/>
-      <c r="I435" s="115"/>
-      <c r="J435" s="115"/>
-      <c r="K435" s="115"/>
-      <c r="L435" s="115"/>
+      <c r="D435" s="112"/>
+      <c r="E435" s="112"/>
+      <c r="F435" s="110"/>
+      <c r="G435" s="110"/>
+      <c r="H435" s="110"/>
+      <c r="I435" s="110"/>
+      <c r="J435" s="110"/>
+      <c r="K435" s="110"/>
+      <c r="L435" s="110"/>
     </row>
     <row r="436" spans="1:12" ht="15">
-      <c r="A436" s="115"/>
-      <c r="B436" s="115"/>
-      <c r="C436" s="120" t="s">
+      <c r="A436" s="110"/>
+      <c r="B436" s="110"/>
+      <c r="C436" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="D436" s="121"/>
-      <c r="E436" s="121"/>
-      <c r="F436" s="121"/>
-      <c r="G436" s="121"/>
-      <c r="H436" s="115"/>
-      <c r="I436" s="115"/>
-      <c r="J436" s="115"/>
-      <c r="K436" s="115"/>
-      <c r="L436" s="115"/>
+      <c r="D436" s="116"/>
+      <c r="E436" s="116"/>
+      <c r="F436" s="116"/>
+      <c r="G436" s="116"/>
+      <c r="H436" s="110"/>
+      <c r="I436" s="110"/>
+      <c r="J436" s="110"/>
+      <c r="K436" s="110"/>
+      <c r="L436" s="110"/>
     </row>
     <row r="437" spans="1:12" ht="15">
-      <c r="A437" s="115"/>
-      <c r="B437" s="115"/>
-      <c r="C437" s="115"/>
-      <c r="D437" s="115"/>
-      <c r="E437" s="115"/>
-      <c r="F437" s="115"/>
-      <c r="G437" s="115"/>
-      <c r="H437" s="115"/>
-      <c r="I437" s="115"/>
-      <c r="J437" s="115"/>
-      <c r="K437" s="115"/>
-      <c r="L437" s="115"/>
+      <c r="A437" s="110"/>
+      <c r="B437" s="110"/>
+      <c r="C437" s="110"/>
+      <c r="D437" s="110"/>
+      <c r="E437" s="110"/>
+      <c r="F437" s="110"/>
+      <c r="G437" s="110"/>
+      <c r="H437" s="110"/>
+      <c r="I437" s="110"/>
+      <c r="J437" s="110"/>
+      <c r="K437" s="110"/>
+      <c r="L437" s="110"/>
     </row>
     <row r="438" spans="1:12" ht="15">
-      <c r="A438" s="115"/>
-      <c r="B438" s="115" t="s">
+      <c r="A438" s="110"/>
+      <c r="B438" s="110" t="s">
         <v>158</v>
       </c>
-      <c r="C438" s="117"/>
-      <c r="D438" s="117"/>
-      <c r="E438" s="117"/>
-      <c r="F438" s="117"/>
-      <c r="G438" s="115"/>
-      <c r="H438" s="115"/>
-      <c r="I438" s="115"/>
-      <c r="J438" s="115"/>
-      <c r="K438" s="115"/>
-      <c r="L438" s="115"/>
+      <c r="C438" s="112"/>
+      <c r="D438" s="112"/>
+      <c r="E438" s="112"/>
+      <c r="F438" s="112"/>
+      <c r="G438" s="110"/>
+      <c r="H438" s="110"/>
+      <c r="I438" s="110"/>
+      <c r="J438" s="110"/>
+      <c r="K438" s="110"/>
+      <c r="L438" s="110"/>
     </row>
     <row r="439" spans="1:12" ht="15">
-      <c r="A439" s="115"/>
-      <c r="B439" s="120" t="s">
+      <c r="A439" s="110"/>
+      <c r="B439" s="115" t="s">
         <v>159</v>
       </c>
-      <c r="C439" s="121"/>
-      <c r="D439" s="121"/>
-      <c r="E439" s="121"/>
-      <c r="F439" s="115"/>
-      <c r="G439" s="115"/>
-      <c r="H439" s="115"/>
-      <c r="I439" s="115"/>
-      <c r="J439" s="115"/>
-      <c r="K439" s="115"/>
-      <c r="L439" s="115"/>
+      <c r="C439" s="116"/>
+      <c r="D439" s="116"/>
+      <c r="E439" s="116"/>
+      <c r="F439" s="110"/>
+      <c r="G439" s="110"/>
+      <c r="H439" s="110"/>
+      <c r="I439" s="110"/>
+      <c r="J439" s="110"/>
+      <c r="K439" s="110"/>
+      <c r="L439" s="110"/>
     </row>
     <row r="440" spans="1:12" ht="15">
-      <c r="A440" s="115"/>
-      <c r="B440" s="115" t="s">
+      <c r="A440" s="110"/>
+      <c r="B440" s="110" t="s">
         <v>160</v>
       </c>
-      <c r="C440" s="117"/>
-      <c r="D440" s="117"/>
-      <c r="E440" s="117"/>
-      <c r="F440" s="115"/>
-      <c r="G440" s="115"/>
-      <c r="H440" s="115"/>
-      <c r="I440" s="115"/>
-      <c r="J440" s="115"/>
-      <c r="K440" s="115"/>
-      <c r="L440" s="115"/>
+      <c r="C440" s="112"/>
+      <c r="D440" s="112"/>
+      <c r="E440" s="112"/>
+      <c r="F440" s="110"/>
+      <c r="G440" s="110"/>
+      <c r="H440" s="110"/>
+      <c r="I440" s="110"/>
+      <c r="J440" s="110"/>
+      <c r="K440" s="110"/>
+      <c r="L440" s="110"/>
     </row>
     <row r="441" spans="1:12" ht="15">
-      <c r="A441" s="115"/>
-      <c r="B441" s="120" t="s">
+      <c r="A441" s="110"/>
+      <c r="B441" s="115" t="s">
         <v>161</v>
       </c>
-      <c r="C441" s="121"/>
-      <c r="D441" s="121"/>
-      <c r="E441" s="121"/>
-      <c r="F441" s="115"/>
-      <c r="G441" s="115"/>
-      <c r="H441" s="115"/>
-      <c r="I441" s="115"/>
-      <c r="J441" s="115"/>
-      <c r="K441" s="115"/>
-      <c r="L441" s="115"/>
+      <c r="C441" s="116"/>
+      <c r="D441" s="116"/>
+      <c r="E441" s="116"/>
+      <c r="F441" s="110"/>
+      <c r="G441" s="110"/>
+      <c r="H441" s="110"/>
+      <c r="I441" s="110"/>
+      <c r="J441" s="110"/>
+      <c r="K441" s="110"/>
+      <c r="L441" s="110"/>
     </row>
     <row r="442" spans="1:12" ht="15">
-      <c r="A442" s="115"/>
-      <c r="B442" s="115"/>
-      <c r="C442" s="115"/>
-      <c r="D442" s="115"/>
-      <c r="E442" s="115"/>
-      <c r="F442" s="115"/>
-      <c r="G442" s="115"/>
-      <c r="H442" s="115"/>
-      <c r="I442" s="115"/>
-      <c r="J442" s="115"/>
-      <c r="K442" s="115"/>
-      <c r="L442" s="115"/>
+      <c r="A442" s="110"/>
+      <c r="B442" s="110"/>
+      <c r="C442" s="110"/>
+      <c r="D442" s="110"/>
+      <c r="E442" s="110"/>
+      <c r="F442" s="110"/>
+      <c r="G442" s="110"/>
+      <c r="H442" s="110"/>
+      <c r="I442" s="110"/>
+      <c r="J442" s="110"/>
+      <c r="K442" s="110"/>
+      <c r="L442" s="110"/>
     </row>
     <row r="443" spans="1:12" ht="15">
-      <c r="A443" s="115"/>
-      <c r="B443" s="115"/>
-      <c r="C443" s="115"/>
-      <c r="D443" s="115"/>
-      <c r="E443" s="115"/>
-      <c r="F443" s="115"/>
-      <c r="G443" s="115"/>
-      <c r="H443" s="115"/>
-      <c r="I443" s="115"/>
-      <c r="J443" s="115"/>
-      <c r="K443" s="115"/>
-      <c r="L443" s="115"/>
+      <c r="A443" s="110"/>
+      <c r="B443" s="110"/>
+      <c r="C443" s="110"/>
+      <c r="D443" s="110"/>
+      <c r="E443" s="110"/>
+      <c r="F443" s="110"/>
+      <c r="G443" s="110"/>
+      <c r="H443" s="110"/>
+      <c r="I443" s="110"/>
+      <c r="J443" s="110"/>
+      <c r="K443" s="110"/>
+      <c r="L443" s="110"/>
     </row>
     <row r="444" spans="1:12" ht="15">
-      <c r="A444" s="115"/>
-      <c r="B444" s="118" t="s">
+      <c r="A444" s="110"/>
+      <c r="B444" s="110"/>
+      <c r="C444" s="110"/>
+      <c r="D444" s="110"/>
+      <c r="E444" s="110"/>
+      <c r="F444" s="110"/>
+      <c r="G444" s="110"/>
+      <c r="H444" s="110"/>
+      <c r="I444" s="110"/>
+      <c r="J444" s="110"/>
+      <c r="K444" s="110"/>
+      <c r="L444" s="110"/>
+    </row>
+    <row r="445" spans="1:12" ht="15">
+      <c r="A445" s="110"/>
+      <c r="B445" s="113" t="s">
         <v>162</v>
       </c>
-      <c r="C444" s="119"/>
-      <c r="D444" s="115"/>
-      <c r="E444" s="115"/>
-      <c r="F444" s="115"/>
-      <c r="G444" s="115"/>
-      <c r="H444" s="115"/>
-      <c r="I444" s="115"/>
-      <c r="J444" s="115"/>
-      <c r="K444" s="115"/>
-      <c r="L444" s="115"/>
-    </row>
-    <row r="445" spans="1:12" ht="15">
-      <c r="A445" s="115"/>
-      <c r="B445" s="115" t="s">
+      <c r="C445" s="114"/>
+      <c r="D445" s="110"/>
+      <c r="E445" s="110"/>
+      <c r="F445" s="110"/>
+      <c r="G445" s="110"/>
+      <c r="H445" s="110"/>
+      <c r="I445" s="110"/>
+      <c r="J445" s="110"/>
+      <c r="K445" s="110"/>
+      <c r="L445" s="110"/>
+    </row>
+    <row r="446" spans="1:12" ht="15">
+      <c r="A446" s="110"/>
+      <c r="B446" s="110" t="s">
         <v>163</v>
       </c>
-      <c r="C445" s="117"/>
-      <c r="D445" s="117"/>
-      <c r="E445" s="115"/>
-      <c r="F445" s="115"/>
-      <c r="G445" s="115"/>
-      <c r="H445" s="115"/>
-      <c r="I445" s="115"/>
-      <c r="J445" s="115"/>
-      <c r="K445" s="115"/>
-      <c r="L445" s="115"/>
-    </row>
-    <row r="446" spans="1:12" ht="15">
-      <c r="A446" s="115"/>
-      <c r="B446" s="122" t="s">
+      <c r="C446" s="112"/>
+      <c r="D446" s="112"/>
+      <c r="E446" s="110"/>
+      <c r="F446" s="110"/>
+      <c r="G446" s="110"/>
+      <c r="H446" s="110"/>
+      <c r="I446" s="110"/>
+      <c r="J446" s="110"/>
+      <c r="K446" s="110"/>
+      <c r="L446" s="110"/>
+    </row>
+    <row r="447" spans="1:12" ht="15">
+      <c r="A447" s="110"/>
+      <c r="B447" s="117" t="s">
         <v>164</v>
       </c>
-      <c r="C446" s="123"/>
-      <c r="D446" s="123"/>
-      <c r="E446" s="115"/>
-      <c r="F446" s="115"/>
-      <c r="G446" s="115"/>
-      <c r="H446" s="115"/>
-      <c r="I446" s="115"/>
-      <c r="J446" s="115"/>
-      <c r="K446" s="115"/>
-      <c r="L446" s="115"/>
-    </row>
-    <row r="448" spans="1:12" ht="15">
-      <c r="B448" s="115" t="s">
+      <c r="C447" s="118"/>
+      <c r="D447" s="118"/>
+      <c r="E447" s="110"/>
+      <c r="F447" s="110"/>
+      <c r="G447" s="110"/>
+      <c r="H447" s="110"/>
+      <c r="I447" s="110"/>
+      <c r="J447" s="110"/>
+      <c r="K447" s="110"/>
+      <c r="L447" s="110"/>
+    </row>
+    <row r="449" spans="2:3" ht="15">
+      <c r="B449" s="110" t="s">
         <v>165</v>
       </c>
-      <c r="C448" s="117"/>
-    </row>
-    <row r="449" spans="2:3" ht="15">
-      <c r="B449" s="115" t="s">
+      <c r="C449" s="112"/>
+    </row>
+    <row r="450" spans="2:3" ht="15">
+      <c r="B450" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="C449" s="117"/>
-    </row>
-    <row r="450" spans="2:3" ht="15">
-      <c r="B450" s="115"/>
-      <c r="C450" s="115"/>
+      <c r="C450" s="112"/>
     </row>
     <row r="451" spans="2:3" ht="15">
-      <c r="B451" s="115" t="s">
+      <c r="B451" s="110"/>
+      <c r="C451" s="110"/>
+    </row>
+    <row r="452" spans="2:3" ht="15">
+      <c r="B452" s="110" t="s">
         <v>167</v>
       </c>
-      <c r="C451" s="117"/>
-    </row>
-    <row r="452" spans="2:3" ht="15">
-      <c r="B452" s="122" t="s">
+      <c r="C452" s="112"/>
+    </row>
+    <row r="453" spans="2:3" ht="15">
+      <c r="B453" s="117" t="s">
         <v>168</v>
       </c>
-      <c r="C452" s="123"/>
+      <c r="C453" s="118"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11"/>
@@ -24527,14 +24542,14 @@
       <c r="C72" s="3"/>
     </row>
     <row r="73" spans="1:11" ht="14.45">
-      <c r="C73" s="110" t="s">
+      <c r="C73" s="123" t="s">
         <v>266</v>
       </c>
-      <c r="D73" s="110"/>
-      <c r="J73" s="111" t="s">
+      <c r="D73" s="123"/>
+      <c r="J73" s="124" t="s">
         <v>267</v>
       </c>
-      <c r="K73" s="111"/>
+      <c r="K73" s="124"/>
     </row>
     <row r="74" spans="1:11">
       <c r="C74" s="3"/>
@@ -24631,10 +24646,10 @@
       <c r="C100" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D100" s="110" t="s">
+      <c r="D100" s="123" t="s">
         <v>266</v>
       </c>
-      <c r="E100" s="110"/>
+      <c r="E100" s="123"/>
     </row>
     <row r="101" spans="2:14">
       <c r="C101" s="3" t="s">
@@ -24750,25 +24765,25 @@
     </row>
     <row r="143" spans="1:17" ht="13.5" customHeight="1"/>
     <row r="144" spans="1:17" ht="21.95" customHeight="1">
-      <c r="A144" s="108" t="s">
+      <c r="A144" s="121" t="s">
         <v>291</v>
       </c>
-      <c r="B144" s="108"/>
-      <c r="C144" s="108"/>
-      <c r="D144" s="108"/>
-      <c r="E144" s="108"/>
-      <c r="F144" s="108"/>
-      <c r="G144" s="108"/>
-      <c r="H144" s="108"/>
-      <c r="I144" s="108"/>
-      <c r="J144" s="108"/>
-      <c r="K144" s="108"/>
-      <c r="L144" s="108"/>
-      <c r="M144" s="108"/>
-      <c r="N144" s="108"/>
-      <c r="O144" s="108"/>
-      <c r="P144" s="108"/>
-      <c r="Q144" s="108"/>
+      <c r="B144" s="121"/>
+      <c r="C144" s="121"/>
+      <c r="D144" s="121"/>
+      <c r="E144" s="121"/>
+      <c r="F144" s="121"/>
+      <c r="G144" s="121"/>
+      <c r="H144" s="121"/>
+      <c r="I144" s="121"/>
+      <c r="J144" s="121"/>
+      <c r="K144" s="121"/>
+      <c r="L144" s="121"/>
+      <c r="M144" s="121"/>
+      <c r="N144" s="121"/>
+      <c r="O144" s="121"/>
+      <c r="P144" s="121"/>
+      <c r="Q144" s="121"/>
     </row>
     <row r="145" spans="1:17" ht="13.5" customHeight="1">
       <c r="A145" s="59" t="s">
@@ -24792,15 +24807,15 @@
       <c r="Q145" s="59"/>
     </row>
     <row r="146" spans="1:17" ht="18.95" customHeight="1">
-      <c r="A146" s="108" t="s">
+      <c r="A146" s="121" t="s">
         <v>293</v>
       </c>
-      <c r="B146" s="108"/>
-      <c r="C146" s="108"/>
-      <c r="D146" s="108"/>
-      <c r="E146" s="108"/>
-      <c r="F146" s="108"/>
-      <c r="G146" s="108"/>
+      <c r="B146" s="121"/>
+      <c r="C146" s="121"/>
+      <c r="D146" s="121"/>
+      <c r="E146" s="121"/>
+      <c r="F146" s="121"/>
+      <c r="G146" s="121"/>
       <c r="H146" s="59"/>
       <c r="I146" s="59"/>
       <c r="J146" s="59"/>
@@ -24816,12 +24831,12 @@
       <c r="A147" s="59" t="s">
         <v>294</v>
       </c>
-      <c r="B147" s="104"/>
-      <c r="C147" s="104"/>
-      <c r="D147" s="104"/>
-      <c r="E147" s="104"/>
-      <c r="F147" s="104"/>
-      <c r="G147" s="104"/>
+      <c r="B147" s="119"/>
+      <c r="C147" s="119"/>
+      <c r="D147" s="119"/>
+      <c r="E147" s="119"/>
+      <c r="F147" s="119"/>
+      <c r="G147" s="119"/>
       <c r="H147" s="59"/>
       <c r="I147" s="59"/>
       <c r="J147" s="59"/>
@@ -24834,23 +24849,23 @@
       <c r="Q147" s="59"/>
     </row>
     <row r="148" spans="1:17" ht="18.95" customHeight="1">
-      <c r="A148" s="108" t="s">
+      <c r="A148" s="121" t="s">
         <v>295</v>
       </c>
-      <c r="B148" s="108"/>
-      <c r="C148" s="108"/>
-      <c r="D148" s="108"/>
-      <c r="E148" s="108"/>
-      <c r="F148" s="108"/>
-      <c r="G148" s="108"/>
-      <c r="H148" s="108"/>
-      <c r="I148" s="108"/>
-      <c r="J148" s="108"/>
-      <c r="K148" s="108"/>
-      <c r="L148" s="108"/>
-      <c r="M148" s="108"/>
-      <c r="N148" s="108"/>
-      <c r="O148" s="108"/>
+      <c r="B148" s="121"/>
+      <c r="C148" s="121"/>
+      <c r="D148" s="121"/>
+      <c r="E148" s="121"/>
+      <c r="F148" s="121"/>
+      <c r="G148" s="121"/>
+      <c r="H148" s="121"/>
+      <c r="I148" s="121"/>
+      <c r="J148" s="121"/>
+      <c r="K148" s="121"/>
+      <c r="L148" s="121"/>
+      <c r="M148" s="121"/>
+      <c r="N148" s="121"/>
+      <c r="O148" s="121"/>
       <c r="P148" s="59"/>
       <c r="Q148" s="59"/>
     </row>
@@ -24858,12 +24873,12 @@
       <c r="A149" s="59" t="s">
         <v>292</v>
       </c>
-      <c r="B149" s="104"/>
-      <c r="C149" s="104"/>
-      <c r="D149" s="104"/>
-      <c r="E149" s="104"/>
-      <c r="F149" s="104"/>
-      <c r="G149" s="104"/>
+      <c r="B149" s="119"/>
+      <c r="C149" s="119"/>
+      <c r="D149" s="119"/>
+      <c r="E149" s="119"/>
+      <c r="F149" s="119"/>
+      <c r="G149" s="119"/>
       <c r="H149" s="59"/>
       <c r="I149" s="59"/>
       <c r="J149" s="59"/>
@@ -24876,36 +24891,36 @@
       <c r="Q149" s="59"/>
     </row>
     <row r="150" spans="1:17" ht="17.45">
-      <c r="A150" s="108" t="s">
+      <c r="A150" s="121" t="s">
         <v>296</v>
       </c>
-      <c r="B150" s="108"/>
-      <c r="C150" s="108"/>
-      <c r="D150" s="108"/>
-      <c r="E150" s="108"/>
-      <c r="F150" s="108"/>
-      <c r="G150" s="108"/>
-      <c r="H150" s="108"/>
-      <c r="I150" s="108"/>
-      <c r="J150" s="108"/>
-      <c r="K150" s="108"/>
-      <c r="L150" s="108"/>
-      <c r="M150" s="108"/>
-      <c r="N150" s="108"/>
-      <c r="O150" s="108"/>
-      <c r="P150" s="108"/>
-      <c r="Q150" s="108"/>
+      <c r="B150" s="121"/>
+      <c r="C150" s="121"/>
+      <c r="D150" s="121"/>
+      <c r="E150" s="121"/>
+      <c r="F150" s="121"/>
+      <c r="G150" s="121"/>
+      <c r="H150" s="121"/>
+      <c r="I150" s="121"/>
+      <c r="J150" s="121"/>
+      <c r="K150" s="121"/>
+      <c r="L150" s="121"/>
+      <c r="M150" s="121"/>
+      <c r="N150" s="121"/>
+      <c r="O150" s="121"/>
+      <c r="P150" s="121"/>
+      <c r="Q150" s="121"/>
     </row>
     <row r="151" spans="1:17" ht="17.45">
       <c r="A151" s="59" t="s">
         <v>297</v>
       </c>
-      <c r="B151" s="104"/>
-      <c r="C151" s="104"/>
-      <c r="D151" s="104"/>
-      <c r="E151" s="104"/>
-      <c r="F151" s="104"/>
-      <c r="G151" s="104"/>
+      <c r="B151" s="119"/>
+      <c r="C151" s="119"/>
+      <c r="D151" s="119"/>
+      <c r="E151" s="119"/>
+      <c r="F151" s="119"/>
+      <c r="G151" s="119"/>
       <c r="H151" s="59"/>
       <c r="I151" s="59"/>
       <c r="J151" s="59"/>
@@ -24915,18 +24930,18 @@
       <c r="N151" s="59"/>
       <c r="O151" s="59"/>
       <c r="P151" s="59"/>
-      <c r="Q151" s="104"/>
+      <c r="Q151" s="119"/>
     </row>
     <row r="152" spans="1:17" ht="17.45" customHeight="1">
-      <c r="A152" s="108" t="s">
+      <c r="A152" s="121" t="s">
         <v>298</v>
       </c>
-      <c r="B152" s="108"/>
-      <c r="C152" s="108"/>
-      <c r="D152" s="108"/>
-      <c r="E152" s="108"/>
-      <c r="F152" s="108"/>
-      <c r="G152" s="108"/>
+      <c r="B152" s="121"/>
+      <c r="C152" s="121"/>
+      <c r="D152" s="121"/>
+      <c r="E152" s="121"/>
+      <c r="F152" s="121"/>
+      <c r="G152" s="121"/>
     </row>
     <row r="153" spans="1:17">
       <c r="A153" s="59" t="s">
@@ -24940,15 +24955,15 @@
       <c r="G153" s="59"/>
     </row>
     <row r="154" spans="1:17" ht="17.45">
-      <c r="A154" s="108" t="s">
+      <c r="A154" s="121" t="s">
         <v>300</v>
       </c>
-      <c r="B154" s="108"/>
-      <c r="C154" s="108"/>
-      <c r="D154" s="108"/>
-      <c r="E154" s="108"/>
-      <c r="F154" s="108"/>
-      <c r="G154" s="108"/>
+      <c r="B154" s="121"/>
+      <c r="C154" s="121"/>
+      <c r="D154" s="121"/>
+      <c r="E154" s="121"/>
+      <c r="F154" s="121"/>
+      <c r="G154" s="121"/>
       <c r="J154" s="59" t="s">
         <v>301</v>
       </c>
@@ -24972,15 +24987,15 @@
       <c r="G155" s="59"/>
     </row>
     <row r="156" spans="1:17" ht="17.45">
-      <c r="A156" s="108" t="s">
+      <c r="A156" s="121" t="s">
         <v>302</v>
       </c>
-      <c r="B156" s="108"/>
-      <c r="C156" s="108"/>
-      <c r="D156" s="108"/>
-      <c r="E156" s="108"/>
-      <c r="F156" s="108"/>
-      <c r="G156" s="108"/>
+      <c r="B156" s="121"/>
+      <c r="C156" s="121"/>
+      <c r="D156" s="121"/>
+      <c r="E156" s="121"/>
+      <c r="F156" s="121"/>
+      <c r="G156" s="121"/>
     </row>
     <row r="157" spans="1:17">
       <c r="A157" s="59" t="s">
@@ -24994,15 +25009,15 @@
       <c r="G157" s="59"/>
     </row>
     <row r="158" spans="1:17" ht="15">
-      <c r="A158" s="109" t="s">
+      <c r="A158" s="122" t="s">
         <v>303</v>
       </c>
-      <c r="B158" s="109"/>
-      <c r="C158" s="109"/>
-      <c r="D158" s="109"/>
-      <c r="E158" s="109"/>
-      <c r="F158" s="109"/>
-      <c r="G158" s="109"/>
+      <c r="B158" s="122"/>
+      <c r="C158" s="122"/>
+      <c r="D158" s="122"/>
+      <c r="E158" s="122"/>
+      <c r="F158" s="122"/>
+      <c r="G158" s="122"/>
     </row>
     <row r="159" spans="1:17">
       <c r="A159" s="59" t="s">
@@ -25016,18 +25031,18 @@
       <c r="G159" s="59"/>
     </row>
     <row r="161" spans="1:31" ht="17.45">
-      <c r="A161" s="108" t="s">
+      <c r="A161" s="121" t="s">
         <v>304</v>
       </c>
-      <c r="B161" s="108"/>
-      <c r="C161" s="108"/>
-      <c r="D161" s="108"/>
-      <c r="E161" s="108"/>
-      <c r="F161" s="108"/>
-      <c r="G161" s="108"/>
-      <c r="H161" s="108"/>
-      <c r="I161" s="108"/>
-      <c r="J161" s="108"/>
+      <c r="B161" s="121"/>
+      <c r="C161" s="121"/>
+      <c r="D161" s="121"/>
+      <c r="E161" s="121"/>
+      <c r="F161" s="121"/>
+      <c r="G161" s="121"/>
+      <c r="H161" s="121"/>
+      <c r="I161" s="121"/>
+      <c r="J161" s="121"/>
       <c r="L161" s="3" t="s">
         <v>305</v>
       </c>
@@ -25050,15 +25065,15 @@
       </c>
     </row>
     <row r="163" spans="1:31" ht="17.45">
-      <c r="A163" s="108" t="s">
+      <c r="A163" s="121" t="s">
         <v>308</v>
       </c>
-      <c r="B163" s="108"/>
-      <c r="C163" s="108"/>
-      <c r="D163" s="108"/>
-      <c r="E163" s="108"/>
-      <c r="F163" s="108"/>
-      <c r="G163" s="108"/>
+      <c r="B163" s="121"/>
+      <c r="C163" s="121"/>
+      <c r="D163" s="121"/>
+      <c r="E163" s="121"/>
+      <c r="F163" s="121"/>
+      <c r="G163" s="121"/>
     </row>
     <row r="164" spans="1:31">
       <c r="A164" s="59"/>
@@ -25070,15 +25085,15 @@
       <c r="G164" s="59"/>
     </row>
     <row r="165" spans="1:31" ht="17.45">
-      <c r="A165" s="108" t="s">
+      <c r="A165" s="121" t="s">
         <v>309</v>
       </c>
-      <c r="B165" s="108"/>
-      <c r="C165" s="108"/>
-      <c r="D165" s="108"/>
-      <c r="E165" s="108"/>
-      <c r="F165" s="108"/>
-      <c r="G165" s="108"/>
+      <c r="B165" s="121"/>
+      <c r="C165" s="121"/>
+      <c r="D165" s="121"/>
+      <c r="E165" s="121"/>
+      <c r="F165" s="121"/>
+      <c r="G165" s="121"/>
     </row>
     <row r="166" spans="1:31">
       <c r="A166" s="59"/>
@@ -25090,15 +25105,15 @@
       <c r="G166" s="59"/>
     </row>
     <row r="167" spans="1:31" s="67" customFormat="1" ht="17.45">
-      <c r="A167" s="108" t="s">
+      <c r="A167" s="121" t="s">
         <v>310</v>
       </c>
-      <c r="B167" s="108"/>
-      <c r="C167" s="108"/>
-      <c r="D167" s="108"/>
-      <c r="E167" s="108"/>
-      <c r="F167" s="108"/>
-      <c r="G167" s="108"/>
+      <c r="B167" s="121"/>
+      <c r="C167" s="121"/>
+      <c r="D167" s="121"/>
+      <c r="E167" s="121"/>
+      <c r="F167" s="121"/>
+      <c r="G167" s="121"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
@@ -25136,15 +25151,15 @@
       <c r="G168" s="59"/>
     </row>
     <row r="169" spans="1:31" ht="17.45">
-      <c r="A169" s="108" t="s">
+      <c r="A169" s="121" t="s">
         <v>312</v>
       </c>
-      <c r="B169" s="108"/>
-      <c r="C169" s="108"/>
-      <c r="D169" s="108"/>
-      <c r="E169" s="108"/>
-      <c r="F169" s="108"/>
-      <c r="G169" s="108"/>
+      <c r="B169" s="121"/>
+      <c r="C169" s="121"/>
+      <c r="D169" s="121"/>
+      <c r="E169" s="121"/>
+      <c r="F169" s="121"/>
+      <c r="G169" s="121"/>
     </row>
     <row r="170" spans="1:31">
       <c r="A170" s="59" t="s">
